--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_pop_step1_Central_African_Republic___CAR_1008_03PM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_pop_step1_Central_African_Republic___CAR_1008_03PM.xlsx
@@ -518,38 +518,38 @@
         <v>594</v>
       </c>
       <c r="D2" t="n">
-        <v>30.4</v>
+        <v>29</v>
       </c>
       <c r="E2" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="F2" t="n">
-        <v>54.5</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="H2" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>37</v>
+      </c>
+      <c r="J2" t="n">
         <v>14.7</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>88</v>
       </c>
-      <c r="J2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K2" t="n">
-        <v>3</v>
-      </c>
       <c r="L2" t="n">
-        <v>69.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="M2" t="n">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -568,34 +568,34 @@
         <v>2134</v>
       </c>
       <c r="D3" t="n">
-        <v>61.3</v>
+        <v>60.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1309</v>
+        <v>1300</v>
       </c>
       <c r="F3" t="n">
-        <v>28.9</v>
+        <v>29.3</v>
       </c>
       <c r="G3" t="n">
-        <v>617</v>
+        <v>626</v>
       </c>
       <c r="H3" t="n">
-        <v>8.4</v>
+        <v>4</v>
       </c>
       <c r="I3" t="n">
-        <v>180</v>
+        <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="K3" t="n">
-        <v>28</v>
+        <v>123</v>
       </c>
       <c r="L3" t="n">
-        <v>38.7</v>
+        <v>39.1</v>
       </c>
       <c r="M3" t="n">
-        <v>825</v>
+        <v>835</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -618,34 +618,34 @@
         <v>2960</v>
       </c>
       <c r="D4" t="n">
-        <v>65.2</v>
+        <v>63.3</v>
       </c>
       <c r="E4" t="n">
-        <v>1928</v>
+        <v>1875</v>
       </c>
       <c r="F4" t="n">
-        <v>24.9</v>
+        <v>28.1</v>
       </c>
       <c r="G4" t="n">
-        <v>737</v>
+        <v>830</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>295</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>254</v>
       </c>
       <c r="L4" t="n">
-        <v>34.8</v>
+        <v>36.7</v>
       </c>
       <c r="M4" t="n">
-        <v>1031</v>
+        <v>1085</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -674,22 +674,22 @@
         <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>40.4</v>
       </c>
       <c r="G5" t="n">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="H5" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="n">
         <v>35.9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>145</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>79.8</v>
@@ -699,7 +699,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -718,34 +718,34 @@
         <v>3857</v>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>52.3</v>
       </c>
       <c r="E6" t="n">
-        <v>2082</v>
+        <v>2018</v>
       </c>
       <c r="F6" t="n">
-        <v>18.4</v>
+        <v>17.6</v>
       </c>
       <c r="G6" t="n">
-        <v>710</v>
+        <v>678</v>
       </c>
       <c r="H6" t="n">
-        <v>27.6</v>
+        <v>10.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1065</v>
+        <v>420</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>742</v>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>47.7</v>
       </c>
       <c r="M6" t="n">
-        <v>1775</v>
+        <v>1840</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -768,34 +768,34 @@
         <v>3595</v>
       </c>
       <c r="D7" t="n">
-        <v>66.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="E7" t="n">
-        <v>2392</v>
+        <v>2346</v>
       </c>
       <c r="F7" t="n">
-        <v>17.5</v>
+        <v>16.2</v>
       </c>
       <c r="G7" t="n">
-        <v>630</v>
+        <v>584</v>
       </c>
       <c r="H7" t="n">
-        <v>15.3</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>549</v>
+        <v>163</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6</v>
+        <v>14</v>
       </c>
       <c r="K7" t="n">
-        <v>23</v>
+        <v>502</v>
       </c>
       <c r="L7" t="n">
-        <v>33.4</v>
+        <v>34.7</v>
       </c>
       <c r="M7" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -818,34 +818,34 @@
         <v>440</v>
       </c>
       <c r="D8" t="n">
-        <v>41.8</v>
+        <v>32.9</v>
       </c>
       <c r="E8" t="n">
-        <v>184</v>
+        <v>145</v>
       </c>
       <c r="F8" t="n">
-        <v>31.2</v>
+        <v>38.7</v>
       </c>
       <c r="G8" t="n">
-        <v>137</v>
+        <v>170</v>
       </c>
       <c r="H8" t="n">
-        <v>25.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1</v>
+        <v>18.7</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="L8" t="n">
-        <v>58.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>256</v>
+        <v>295</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -868,38 +868,38 @@
         <v>1272</v>
       </c>
       <c r="D9" t="n">
-        <v>49.4</v>
+        <v>42.2</v>
       </c>
       <c r="E9" t="n">
-        <v>629</v>
+        <v>537</v>
       </c>
       <c r="F9" t="n">
-        <v>35.6</v>
+        <v>33.9</v>
       </c>
       <c r="G9" t="n">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="H9" t="n">
-        <v>14.4</v>
+        <v>10.6</v>
       </c>
       <c r="I9" t="n">
-        <v>184</v>
+        <v>134</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6</v>
+        <v>13.3</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>170</v>
       </c>
       <c r="L9" t="n">
-        <v>50.6</v>
+        <v>57.8</v>
       </c>
       <c r="M9" t="n">
-        <v>643</v>
+        <v>735</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -918,34 +918,34 @@
         <v>6193</v>
       </c>
       <c r="D10" t="n">
-        <v>35.8</v>
+        <v>35.4</v>
       </c>
       <c r="E10" t="n">
-        <v>2218</v>
+        <v>2191</v>
       </c>
       <c r="F10" t="n">
-        <v>59.8</v>
+        <v>53.7</v>
       </c>
       <c r="G10" t="n">
-        <v>3705</v>
+        <v>3327</v>
       </c>
       <c r="H10" t="n">
-        <v>3.9</v>
+        <v>7.9</v>
       </c>
       <c r="I10" t="n">
-        <v>243</v>
+        <v>487</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>27</v>
+        <v>189</v>
       </c>
       <c r="L10" t="n">
-        <v>64.2</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>3976</v>
+        <v>4003</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -968,34 +968,34 @@
         <v>3044</v>
       </c>
       <c r="D11" t="n">
-        <v>44.5</v>
+        <v>43.2</v>
       </c>
       <c r="E11" t="n">
-        <v>1355</v>
+        <v>1316</v>
       </c>
       <c r="F11" t="n">
-        <v>40.3</v>
+        <v>37.7</v>
       </c>
       <c r="G11" t="n">
-        <v>1227</v>
+        <v>1149</v>
       </c>
       <c r="H11" t="n">
-        <v>15.2</v>
+        <v>5.2</v>
       </c>
       <c r="I11" t="n">
-        <v>462</v>
+        <v>157</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>422</v>
       </c>
       <c r="L11" t="n">
-        <v>55.5</v>
+        <v>56.8</v>
       </c>
       <c r="M11" t="n">
-        <v>1689</v>
+        <v>1728</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1018,34 +1018,34 @@
         <v>2062</v>
       </c>
       <c r="D12" t="n">
-        <v>61.1</v>
+        <v>58.9</v>
       </c>
       <c r="E12" t="n">
-        <v>1260</v>
+        <v>1214</v>
       </c>
       <c r="F12" t="n">
-        <v>34.8</v>
+        <v>35.9</v>
       </c>
       <c r="G12" t="n">
-        <v>718</v>
+        <v>741</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>1.9</v>
       </c>
       <c r="I12" t="n">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="L12" t="n">
-        <v>38.9</v>
+        <v>41.1</v>
       </c>
       <c r="M12" t="n">
-        <v>802</v>
+        <v>848</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1068,34 +1068,34 @@
         <v>2076</v>
       </c>
       <c r="D13" t="n">
-        <v>52.2</v>
+        <v>51.6</v>
       </c>
       <c r="E13" t="n">
-        <v>1085</v>
+        <v>1070</v>
       </c>
       <c r="F13" t="n">
-        <v>33.6</v>
+        <v>33.9</v>
       </c>
       <c r="G13" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="H13" t="n">
-        <v>13.1</v>
+        <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>273</v>
+        <v>57</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>11.8</v>
       </c>
       <c r="K13" t="n">
-        <v>22</v>
+        <v>244</v>
       </c>
       <c r="L13" t="n">
-        <v>47.8</v>
+        <v>48.4</v>
       </c>
       <c r="M13" t="n">
-        <v>991</v>
+        <v>1006</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1124,22 +1124,22 @@
         <v>6214</v>
       </c>
       <c r="F14" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1889</v>
+        <v>1931</v>
       </c>
       <c r="H14" t="n">
-        <v>12.6</v>
+        <v>2.2</v>
       </c>
       <c r="I14" t="n">
-        <v>1176</v>
+        <v>210</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9</v>
+        <v>10.8</v>
       </c>
       <c r="K14" t="n">
-        <v>84</v>
+        <v>1008</v>
       </c>
       <c r="L14" t="n">
         <v>33.6</v>
@@ -1168,38 +1168,38 @@
         <v>4921</v>
       </c>
       <c r="D15" t="n">
-        <v>50.3</v>
+        <v>48.1</v>
       </c>
       <c r="E15" t="n">
-        <v>2474</v>
+        <v>2366</v>
       </c>
       <c r="F15" t="n">
-        <v>24.3</v>
+        <v>23.2</v>
       </c>
       <c r="G15" t="n">
-        <v>1196</v>
+        <v>1142</v>
       </c>
       <c r="H15" t="n">
-        <v>24.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>1224</v>
+        <v>408</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>20.4</v>
       </c>
       <c r="K15" t="n">
-        <v>27</v>
+        <v>1006</v>
       </c>
       <c r="L15" t="n">
-        <v>49.7</v>
+        <v>51.9</v>
       </c>
       <c r="M15" t="n">
-        <v>2447</v>
+        <v>2556</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1218,38 +1218,38 @@
         <v>4272</v>
       </c>
       <c r="D16" t="n">
-        <v>34.7</v>
+        <v>34.3</v>
       </c>
       <c r="E16" t="n">
-        <v>1481</v>
+        <v>1464</v>
       </c>
       <c r="F16" t="n">
-        <v>37.8</v>
+        <v>39.4</v>
       </c>
       <c r="G16" t="n">
-        <v>1617</v>
+        <v>1685</v>
       </c>
       <c r="H16" t="n">
-        <v>27.1</v>
+        <v>2.8</v>
       </c>
       <c r="I16" t="n">
-        <v>1157</v>
+        <v>119</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>23.5</v>
       </c>
       <c r="K16" t="n">
-        <v>17</v>
+        <v>1004</v>
       </c>
       <c r="L16" t="n">
-        <v>65.3</v>
+        <v>65.7</v>
       </c>
       <c r="M16" t="n">
-        <v>2792</v>
+        <v>2809</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1268,34 +1268,34 @@
         <v>1080</v>
       </c>
       <c r="D17" t="n">
-        <v>37.2</v>
+        <v>36.2</v>
       </c>
       <c r="E17" t="n">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="F17" t="n">
-        <v>36.7</v>
+        <v>40.6</v>
       </c>
       <c r="G17" t="n">
-        <v>396</v>
+        <v>438</v>
       </c>
       <c r="H17" t="n">
-        <v>25.6</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
-        <v>276</v>
+        <v>37</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5</v>
+        <v>19.8</v>
       </c>
       <c r="K17" t="n">
-        <v>5</v>
+        <v>214</v>
       </c>
       <c r="L17" t="n">
-        <v>62.8</v>
+        <v>63.8</v>
       </c>
       <c r="M17" t="n">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1318,38 +1318,38 @@
         <v>4010</v>
       </c>
       <c r="D18" t="n">
-        <v>44.9</v>
+        <v>40.4</v>
       </c>
       <c r="E18" t="n">
-        <v>1800</v>
+        <v>1618</v>
       </c>
       <c r="F18" t="n">
-        <v>39.5</v>
+        <v>36.3</v>
       </c>
       <c r="G18" t="n">
-        <v>1582</v>
+        <v>1455</v>
       </c>
       <c r="H18" t="n">
-        <v>15.6</v>
+        <v>10.9</v>
       </c>
       <c r="I18" t="n">
-        <v>627</v>
+        <v>436</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="L18" t="n">
-        <v>55.1</v>
+        <v>59.6</v>
       </c>
       <c r="M18" t="n">
-        <v>2209</v>
+        <v>2391</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1368,34 +1368,34 @@
         <v>210</v>
       </c>
       <c r="D19" t="n">
-        <v>61.5</v>
+        <v>60.6</v>
       </c>
       <c r="E19" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F19" t="n">
-        <v>25.9</v>
+        <v>25.2</v>
       </c>
       <c r="G19" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H19" t="n">
-        <v>12.6</v>
+        <v>3.2</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="L19" t="n">
-        <v>38.5</v>
+        <v>39.4</v>
       </c>
       <c r="M19" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1418,38 +1418,38 @@
         <v>334</v>
       </c>
       <c r="D20" t="n">
-        <v>46.2</v>
+        <v>45.9</v>
       </c>
       <c r="E20" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F20" t="n">
-        <v>34.8</v>
+        <v>27.2</v>
       </c>
       <c r="G20" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="H20" t="n">
-        <v>17.6</v>
+        <v>12.9</v>
       </c>
       <c r="I20" t="n">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="L20" t="n">
-        <v>53.8</v>
+        <v>54.1</v>
       </c>
       <c r="M20" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1474,22 +1474,22 @@
         <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>32.6</v>
+        <v>27.9</v>
       </c>
       <c r="G21" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H21" t="n">
-        <v>19.1</v>
+        <v>10.3</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6</v>
+        <v>14.1</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="L21" t="n">
         <v>52.2</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1518,38 +1518,38 @@
         <v>855</v>
       </c>
       <c r="D22" t="n">
-        <v>41.8</v>
+        <v>38.1</v>
       </c>
       <c r="E22" t="n">
-        <v>357</v>
+        <v>326</v>
       </c>
       <c r="F22" t="n">
-        <v>45.4</v>
+        <v>40.5</v>
       </c>
       <c r="G22" t="n">
-        <v>388</v>
+        <v>347</v>
       </c>
       <c r="H22" t="n">
-        <v>12.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6</v>
+        <v>11.6</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="L22" t="n">
-        <v>58.2</v>
+        <v>61.9</v>
       </c>
       <c r="M22" t="n">
-        <v>498</v>
+        <v>529</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1568,34 +1568,34 @@
         <v>658</v>
       </c>
       <c r="D23" t="n">
-        <v>74.7</v>
+        <v>74</v>
       </c>
       <c r="E23" t="n">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="F23" t="n">
-        <v>19.1</v>
+        <v>17.4</v>
       </c>
       <c r="G23" t="n">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="I23" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L23" t="n">
-        <v>25.3</v>
+        <v>26</v>
       </c>
       <c r="M23" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -1624,22 +1624,22 @@
         <v>1486</v>
       </c>
       <c r="F24" t="n">
-        <v>23.6</v>
+        <v>24.5</v>
       </c>
       <c r="G24" t="n">
-        <v>713</v>
+        <v>739</v>
       </c>
       <c r="H24" t="n">
-        <v>25.9</v>
+        <v>1.7</v>
       </c>
       <c r="I24" t="n">
-        <v>782</v>
+        <v>52</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2</v>
+        <v>24.5</v>
       </c>
       <c r="K24" t="n">
-        <v>35</v>
+        <v>739</v>
       </c>
       <c r="L24" t="n">
         <v>50.7</v>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1668,38 +1668,38 @@
         <v>705</v>
       </c>
       <c r="D25" t="n">
-        <v>47</v>
+        <v>46.5</v>
       </c>
       <c r="E25" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F25" t="n">
-        <v>21.7</v>
+        <v>23.2</v>
       </c>
       <c r="G25" t="n">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="H25" t="n">
-        <v>30.3</v>
+        <v>1.5</v>
       </c>
       <c r="I25" t="n">
-        <v>213</v>
+        <v>11</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>28.8</v>
       </c>
       <c r="K25" t="n">
-        <v>7</v>
+        <v>203</v>
       </c>
       <c r="L25" t="n">
-        <v>53</v>
+        <v>53.5</v>
       </c>
       <c r="M25" t="n">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1718,38 +1718,38 @@
         <v>1671</v>
       </c>
       <c r="D26" t="n">
-        <v>19.2</v>
+        <v>15.6</v>
       </c>
       <c r="E26" t="n">
-        <v>320</v>
+        <v>260</v>
       </c>
       <c r="F26" t="n">
-        <v>45.1</v>
+        <v>34.4</v>
       </c>
       <c r="G26" t="n">
-        <v>754</v>
+        <v>575</v>
       </c>
       <c r="H26" t="n">
-        <v>35.1</v>
+        <v>19.5</v>
       </c>
       <c r="I26" t="n">
-        <v>586</v>
+        <v>325</v>
       </c>
       <c r="J26" t="n">
-        <v>0.6</v>
+        <v>30.5</v>
       </c>
       <c r="K26" t="n">
-        <v>11</v>
+        <v>510</v>
       </c>
       <c r="L26" t="n">
-        <v>80.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>1351</v>
+        <v>1410</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1768,34 +1768,34 @@
         <v>5296</v>
       </c>
       <c r="D27" t="n">
-        <v>65.2</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>3455</v>
+        <v>3439</v>
       </c>
       <c r="F27" t="n">
-        <v>23.2</v>
+        <v>22.6</v>
       </c>
       <c r="G27" t="n">
-        <v>1227</v>
+        <v>1195</v>
       </c>
       <c r="H27" t="n">
-        <v>11.6</v>
+        <v>1.5</v>
       </c>
       <c r="I27" t="n">
-        <v>614</v>
+        <v>81</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>581</v>
       </c>
       <c r="L27" t="n">
-        <v>34.8</v>
+        <v>35.1</v>
       </c>
       <c r="M27" t="n">
-        <v>1841</v>
+        <v>1857</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -1818,10 +1818,10 @@
         <v>1239</v>
       </c>
       <c r="D28" t="n">
-        <v>77</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="F28" t="n">
         <v>14.9</v>
@@ -1830,22 +1830,22 @@
         <v>185</v>
       </c>
       <c r="H28" t="n">
-        <v>8.199999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="I28" t="n">
-        <v>101</v>
+        <v>9</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="L28" t="n">
-        <v>23</v>
+        <v>23.4</v>
       </c>
       <c r="M28" t="n">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -1868,34 +1868,34 @@
         <v>11209</v>
       </c>
       <c r="D29" t="n">
-        <v>65.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>7373</v>
+        <v>7297</v>
       </c>
       <c r="F29" t="n">
-        <v>24.8</v>
+        <v>21.5</v>
       </c>
       <c r="G29" t="n">
-        <v>2784</v>
+        <v>2407</v>
       </c>
       <c r="H29" t="n">
-        <v>9.4</v>
+        <v>4.7</v>
       </c>
       <c r="I29" t="n">
-        <v>1053</v>
+        <v>527</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>978</v>
       </c>
       <c r="L29" t="n">
-        <v>34.2</v>
+        <v>34.9</v>
       </c>
       <c r="M29" t="n">
-        <v>3837</v>
+        <v>3912</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -1918,38 +1918,38 @@
         <v>3668</v>
       </c>
       <c r="D30" t="n">
-        <v>43.2</v>
+        <v>41.3</v>
       </c>
       <c r="E30" t="n">
-        <v>1585</v>
+        <v>1514</v>
       </c>
       <c r="F30" t="n">
-        <v>27.7</v>
+        <v>22.6</v>
       </c>
       <c r="G30" t="n">
-        <v>1018</v>
+        <v>828</v>
       </c>
       <c r="H30" t="n">
-        <v>28.4</v>
+        <v>16.1</v>
       </c>
       <c r="I30" t="n">
-        <v>1041</v>
+        <v>592</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>24</v>
+        <v>734</v>
       </c>
       <c r="L30" t="n">
-        <v>56.8</v>
+        <v>58.7</v>
       </c>
       <c r="M30" t="n">
-        <v>2082</v>
+        <v>2153</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1968,34 +1968,34 @@
         <v>6054</v>
       </c>
       <c r="D31" t="n">
-        <v>74.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>4498</v>
+        <v>4295</v>
       </c>
       <c r="F31" t="n">
-        <v>18.4</v>
+        <v>20.1</v>
       </c>
       <c r="G31" t="n">
-        <v>1116</v>
+        <v>1218</v>
       </c>
       <c r="H31" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="I31" t="n">
-        <v>406</v>
+        <v>203</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6</v>
+        <v>5.6</v>
       </c>
       <c r="K31" t="n">
-        <v>34</v>
+        <v>338</v>
       </c>
       <c r="L31" t="n">
-        <v>25.7</v>
+        <v>29.1</v>
       </c>
       <c r="M31" t="n">
-        <v>1556</v>
+        <v>1759</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
@@ -2018,34 +2018,34 @@
         <v>3717</v>
       </c>
       <c r="D32" t="n">
-        <v>67.3</v>
+        <v>66.7</v>
       </c>
       <c r="E32" t="n">
-        <v>2502</v>
+        <v>2478</v>
       </c>
       <c r="F32" t="n">
-        <v>26.3</v>
+        <v>27.6</v>
       </c>
       <c r="G32" t="n">
-        <v>977</v>
+        <v>1025</v>
       </c>
       <c r="H32" t="n">
-        <v>5.8</v>
+        <v>1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>214</v>
+        <v>48</v>
       </c>
       <c r="J32" t="n">
-        <v>0.6</v>
+        <v>4.5</v>
       </c>
       <c r="K32" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="L32" t="n">
-        <v>32.7</v>
+        <v>33.3</v>
       </c>
       <c r="M32" t="n">
-        <v>1215</v>
+        <v>1239</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -2068,34 +2068,34 @@
         <v>554</v>
       </c>
       <c r="D33" t="n">
-        <v>61</v>
+        <v>60.6</v>
       </c>
       <c r="E33" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F33" t="n">
-        <v>36.9</v>
+        <v>37.6</v>
       </c>
       <c r="G33" t="n">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="H33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L33" t="n">
-        <v>39</v>
+        <v>39.4</v>
       </c>
       <c r="M33" t="n">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
@@ -2118,34 +2118,34 @@
         <v>5660</v>
       </c>
       <c r="D34" t="n">
-        <v>69.8</v>
+        <v>69.5</v>
       </c>
       <c r="E34" t="n">
-        <v>3949</v>
+        <v>3933</v>
       </c>
       <c r="F34" t="n">
-        <v>12.7</v>
+        <v>16.1</v>
       </c>
       <c r="G34" t="n">
-        <v>720</v>
+        <v>911</v>
       </c>
       <c r="H34" t="n">
-        <v>17.5</v>
+        <v>0.3</v>
       </c>
       <c r="I34" t="n">
-        <v>991</v>
+        <v>16</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>14.1</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="L34" t="n">
-        <v>30.2</v>
+        <v>30.5</v>
       </c>
       <c r="M34" t="n">
-        <v>1711</v>
+        <v>1727</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -2168,34 +2168,34 @@
         <v>1005</v>
       </c>
       <c r="D35" t="n">
-        <v>36.9</v>
+        <v>35.6</v>
       </c>
       <c r="E35" t="n">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="F35" t="n">
-        <v>49.1</v>
+        <v>47.7</v>
       </c>
       <c r="G35" t="n">
-        <v>493</v>
+        <v>480</v>
       </c>
       <c r="H35" t="n">
-        <v>13.5</v>
+        <v>5</v>
       </c>
       <c r="I35" t="n">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5</v>
+        <v>11.7</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="L35" t="n">
-        <v>63.1</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -2218,34 +2218,34 @@
         <v>61</v>
       </c>
       <c r="D36" t="n">
-        <v>50.4</v>
+        <v>48.8</v>
       </c>
       <c r="E36" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="G36" t="n">
+        <v>14</v>
+      </c>
+      <c r="H36" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="I36" t="n">
+        <v>6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="K36" t="n">
+        <v>11</v>
+      </c>
+      <c r="L36" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="M36" t="n">
         <v>31</v>
-      </c>
-      <c r="F36" t="n">
-        <v>28.7</v>
-      </c>
-      <c r="G36" t="n">
-        <v>17</v>
-      </c>
-      <c r="H36" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="I36" t="n">
-        <v>12</v>
-      </c>
-      <c r="J36" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K36" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="M36" t="n">
-        <v>30</v>
       </c>
       <c r="N36" t="inlineStr">
         <is>
@@ -2268,38 +2268,38 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>63</v>
+        <v>61.6</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>13</v>
+        <v>10.6</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>23.6</v>
+        <v>4.6</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5</v>
+        <v>23.1</v>
       </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>37</v>
+        <v>38.4</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2318,38 +2318,38 @@
         <v>2485</v>
       </c>
       <c r="D38" t="n">
-        <v>37.3</v>
+        <v>34.2</v>
       </c>
       <c r="E38" t="n">
-        <v>927</v>
+        <v>850</v>
       </c>
       <c r="F38" t="n">
-        <v>35.3</v>
+        <v>34.2</v>
       </c>
       <c r="G38" t="n">
-        <v>878</v>
+        <v>850</v>
       </c>
       <c r="H38" t="n">
-        <v>25.9</v>
+        <v>7.4</v>
       </c>
       <c r="I38" t="n">
-        <v>644</v>
+        <v>184</v>
       </c>
       <c r="J38" t="n">
-        <v>1.4</v>
+        <v>24.2</v>
       </c>
       <c r="K38" t="n">
-        <v>35</v>
+        <v>602</v>
       </c>
       <c r="L38" t="n">
-        <v>62.7</v>
+        <v>65.8</v>
       </c>
       <c r="M38" t="n">
-        <v>1558</v>
+        <v>1636</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>68.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
@@ -2380,19 +2380,19 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>18.4</v>
+        <v>4.3</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>14.4</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>31.1</v>
+        <v>31.4</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -2424,10 +2424,10 @@
         <v>1902</v>
       </c>
       <c r="F40" t="n">
-        <v>26.5</v>
+        <v>22.4</v>
       </c>
       <c r="G40" t="n">
-        <v>747</v>
+        <v>631</v>
       </c>
       <c r="H40" t="n">
         <v>5.5</v>
@@ -2436,10 +2436,10 @@
         <v>154</v>
       </c>
       <c r="J40" t="n">
-        <v>0.5</v>
+        <v>4.6</v>
       </c>
       <c r="K40" t="n">
-        <v>15</v>
+        <v>131</v>
       </c>
       <c r="L40" t="n">
         <v>32.5</v>
@@ -2468,34 +2468,34 @@
         <v>6458</v>
       </c>
       <c r="D41" t="n">
-        <v>51.6</v>
+        <v>48.7</v>
       </c>
       <c r="E41" t="n">
-        <v>3334</v>
+        <v>3145</v>
       </c>
       <c r="F41" t="n">
-        <v>28.9</v>
+        <v>34.7</v>
       </c>
       <c r="G41" t="n">
-        <v>1866</v>
+        <v>2244</v>
       </c>
       <c r="H41" t="n">
-        <v>18.5</v>
+        <v>0.6</v>
       </c>
       <c r="I41" t="n">
-        <v>1195</v>
+        <v>42</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>15.9</v>
       </c>
       <c r="K41" t="n">
-        <v>63</v>
+        <v>1027</v>
       </c>
       <c r="L41" t="n">
-        <v>48.4</v>
+        <v>51.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3124</v>
+        <v>3313</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -2530,16 +2530,16 @@
         <v>888</v>
       </c>
       <c r="H42" t="n">
-        <v>18.9</v>
+        <v>2.7</v>
       </c>
       <c r="I42" t="n">
-        <v>497</v>
+        <v>71</v>
       </c>
       <c r="J42" t="n">
-        <v>0.3</v>
+        <v>16.5</v>
       </c>
       <c r="K42" t="n">
-        <v>7</v>
+        <v>433</v>
       </c>
       <c r="L42" t="n">
         <v>53</v>
@@ -2568,34 +2568,34 @@
         <v>389</v>
       </c>
       <c r="D43" t="n">
-        <v>48.5</v>
+        <v>44.8</v>
       </c>
       <c r="E43" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F43" t="n">
-        <v>29.9</v>
+        <v>34.1</v>
       </c>
       <c r="G43" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="H43" t="n">
-        <v>20.6</v>
+        <v>1.1</v>
       </c>
       <c r="I43" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="J43" t="n">
-        <v>1.1</v>
+        <v>20</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>78</v>
       </c>
       <c r="L43" t="n">
-        <v>51.5</v>
+        <v>55.2</v>
       </c>
       <c r="M43" t="n">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -2618,34 +2618,34 @@
         <v>1154</v>
       </c>
       <c r="D44" t="n">
-        <v>66.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="F44" t="n">
-        <v>20.9</v>
+        <v>19.3</v>
       </c>
       <c r="G44" t="n">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="H44" t="n">
-        <v>12.3</v>
+        <v>3.5</v>
       </c>
       <c r="I44" t="n">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="L44" t="n">
-        <v>33.2</v>
+        <v>33.4</v>
       </c>
       <c r="M44" t="n">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -2668,38 +2668,38 @@
         <v>566</v>
       </c>
       <c r="D45" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="E45" t="n">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F45" t="n">
-        <v>41.3</v>
+        <v>37.2</v>
       </c>
       <c r="G45" t="n">
-        <v>234</v>
+        <v>211</v>
       </c>
       <c r="H45" t="n">
-        <v>30</v>
+        <v>8.5</v>
       </c>
       <c r="I45" t="n">
-        <v>170</v>
+        <v>48</v>
       </c>
       <c r="J45" t="n">
-        <v>0.4</v>
+        <v>27.4</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>155</v>
       </c>
       <c r="L45" t="n">
-        <v>71.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2718,34 +2718,34 @@
         <v>2317</v>
       </c>
       <c r="D46" t="n">
-        <v>67.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>1574</v>
+        <v>1566</v>
       </c>
       <c r="F46" t="n">
-        <v>18.5</v>
+        <v>17.4</v>
       </c>
       <c r="G46" t="n">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="H46" t="n">
-        <v>13.6</v>
+        <v>2.1</v>
       </c>
       <c r="I46" t="n">
-        <v>315</v>
+        <v>48</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>12.9</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="L46" t="n">
-        <v>32.1</v>
+        <v>32.4</v>
       </c>
       <c r="M46" t="n">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -2768,34 +2768,34 @@
         <v>2994</v>
       </c>
       <c r="D47" t="n">
-        <v>53.6</v>
+        <v>52</v>
       </c>
       <c r="E47" t="n">
-        <v>1604</v>
+        <v>1558</v>
       </c>
       <c r="F47" t="n">
-        <v>35.2</v>
+        <v>34.7</v>
       </c>
       <c r="G47" t="n">
-        <v>1054</v>
+        <v>1039</v>
       </c>
       <c r="H47" t="n">
-        <v>10.7</v>
+        <v>5.6</v>
       </c>
       <c r="I47" t="n">
-        <v>321</v>
+        <v>168</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5</v>
+        <v>7.7</v>
       </c>
       <c r="K47" t="n">
-        <v>15</v>
+        <v>229</v>
       </c>
       <c r="L47" t="n">
-        <v>46.4</v>
+        <v>48</v>
       </c>
       <c r="M47" t="n">
-        <v>1390</v>
+        <v>1436</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -2824,22 +2824,22 @@
         <v>504</v>
       </c>
       <c r="F48" t="n">
-        <v>34.9</v>
+        <v>22.1</v>
       </c>
       <c r="G48" t="n">
-        <v>560</v>
+        <v>355</v>
       </c>
       <c r="H48" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="I48" t="n">
+        <v>205</v>
+      </c>
+      <c r="J48" t="n">
         <v>33.7</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>542</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
       </c>
       <c r="L48" t="n">
         <v>68.59999999999999</v>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2868,38 +2868,38 @@
         <v>0</v>
       </c>
       <c r="D49" t="n">
-        <v>27.8</v>
+        <v>26.6</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>46.8</v>
+        <v>22.8</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
+        <v>26.6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
         <v>24.1</v>
       </c>
-      <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="n">
-        <v>1.3</v>
-      </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>72.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="M49" t="n">
         <v>0</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2918,34 +2918,34 @@
         <v>18069</v>
       </c>
       <c r="D50" t="n">
-        <v>62.9</v>
+        <v>54.5</v>
       </c>
       <c r="E50" t="n">
-        <v>11367</v>
+        <v>9856</v>
       </c>
       <c r="F50" t="n">
-        <v>29.8</v>
+        <v>37.5</v>
       </c>
       <c r="G50" t="n">
-        <v>5388</v>
+        <v>6768</v>
       </c>
       <c r="H50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I50" t="n">
+        <v>197</v>
+      </c>
+      <c r="J50" t="n">
         <v>6.9</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>1248</v>
       </c>
-      <c r="J50" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K50" t="n">
-        <v>66</v>
-      </c>
       <c r="L50" t="n">
-        <v>37.1</v>
+        <v>45.5</v>
       </c>
       <c r="M50" t="n">
-        <v>6702</v>
+        <v>8213</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -3060,22 +3060,22 @@
         <v>374</v>
       </c>
       <c r="F2" t="n">
-        <v>53.3</v>
+        <v>48.9</v>
       </c>
       <c r="G2" t="n">
-        <v>592</v>
+        <v>544</v>
       </c>
       <c r="H2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="J2" t="n">
         <v>12</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>133</v>
-      </c>
-      <c r="J2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K2" t="n">
-        <v>12</v>
       </c>
       <c r="L2" t="n">
         <v>66.3</v>
@@ -3110,22 +3110,22 @@
         <v>1954</v>
       </c>
       <c r="F3" t="n">
-        <v>23.5</v>
+        <v>24.7</v>
       </c>
       <c r="G3" t="n">
-        <v>688</v>
+        <v>724</v>
       </c>
       <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>8.6</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>253</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>36</v>
       </c>
       <c r="L3" t="n">
         <v>33.3</v>
@@ -3160,22 +3160,22 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>53.8</v>
+        <v>23.1</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="H4" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>47</v>
+      </c>
+      <c r="J4" t="n">
         <v>43.6</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>67</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>97.40000000000001</v>
@@ -3185,7 +3185,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3204,10 +3204,10 @@
         <v>841</v>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>47.8</v>
       </c>
       <c r="E5" t="n">
-        <v>421</v>
+        <v>402</v>
       </c>
       <c r="F5" t="n">
         <v>13.3</v>
@@ -3216,26 +3216,26 @@
         <v>112</v>
       </c>
       <c r="H5" t="n">
-        <v>36.7</v>
+        <v>6.7</v>
       </c>
       <c r="I5" t="n">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>32.2</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="L5" t="n">
-        <v>50</v>
+        <v>52.2</v>
       </c>
       <c r="M5" t="n">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3254,38 +3254,38 @@
         <v>1178</v>
       </c>
       <c r="D6" t="n">
-        <v>51.2</v>
+        <v>50.4</v>
       </c>
       <c r="E6" t="n">
-        <v>603</v>
+        <v>594</v>
       </c>
       <c r="F6" t="n">
-        <v>18.6</v>
+        <v>22.5</v>
       </c>
       <c r="G6" t="n">
-        <v>219</v>
+        <v>265</v>
       </c>
       <c r="H6" t="n">
-        <v>27.9</v>
+        <v>2.3</v>
       </c>
       <c r="I6" t="n">
-        <v>329</v>
+        <v>27</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3</v>
+        <v>24.8</v>
       </c>
       <c r="K6" t="n">
-        <v>27</v>
+        <v>292</v>
       </c>
       <c r="L6" t="n">
-        <v>48.8</v>
+        <v>49.6</v>
       </c>
       <c r="M6" t="n">
-        <v>575</v>
+        <v>585</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3304,16 +3304,16 @@
         <v>287</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9</v>
+        <v>27.7</v>
       </c>
       <c r="E7" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>48.9</v>
+        <v>40.4</v>
       </c>
       <c r="G7" t="n">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="H7" t="n">
         <v>19.1</v>
@@ -3322,20 +3322,20 @@
         <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>12.8</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="L7" t="n">
-        <v>68.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="M7" t="n">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3360,22 +3360,22 @@
         <v>211</v>
       </c>
       <c r="F8" t="n">
-        <v>49.2</v>
+        <v>32.2</v>
       </c>
       <c r="G8" t="n">
-        <v>437</v>
+        <v>286</v>
       </c>
       <c r="H8" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="I8" t="n">
+        <v>151</v>
+      </c>
+      <c r="J8" t="n">
         <v>27.1</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>241</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>76.3</v>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3410,22 +3410,22 @@
         <v>2224</v>
       </c>
       <c r="F9" t="n">
-        <v>50.4</v>
+        <v>48.7</v>
       </c>
       <c r="G9" t="n">
-        <v>2866</v>
+        <v>2767</v>
       </c>
       <c r="H9" t="n">
-        <v>9.6</v>
+        <v>4.3</v>
       </c>
       <c r="I9" t="n">
-        <v>544</v>
+        <v>247</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>7.8</v>
       </c>
       <c r="K9" t="n">
-        <v>49</v>
+        <v>445</v>
       </c>
       <c r="L9" t="n">
         <v>60.9</v>
@@ -3460,22 +3460,22 @@
         <v>1300</v>
       </c>
       <c r="F10" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="G10" t="n">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="H10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="I10" t="n">
+        <v>57</v>
+      </c>
+      <c r="J10" t="n">
         <v>10</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>170</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>23.3</v>
@@ -3504,34 +3504,34 @@
         <v>1880</v>
       </c>
       <c r="D11" t="n">
-        <v>50.7</v>
+        <v>46.6</v>
       </c>
       <c r="E11" t="n">
-        <v>953</v>
+        <v>875</v>
       </c>
       <c r="F11" t="n">
-        <v>42.5</v>
+        <v>41.1</v>
       </c>
       <c r="G11" t="n">
-        <v>798</v>
+        <v>772</v>
       </c>
       <c r="H11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>103</v>
+      </c>
+      <c r="J11" t="n">
         <v>6.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>129</v>
       </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
-        <v>49.3</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="n">
-        <v>927</v>
+        <v>1004</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -3554,34 +3554,34 @@
         <v>2289</v>
       </c>
       <c r="D12" t="n">
-        <v>53.2</v>
+        <v>51.6</v>
       </c>
       <c r="E12" t="n">
-        <v>1218</v>
+        <v>1181</v>
       </c>
       <c r="F12" t="n">
-        <v>24.2</v>
+        <v>25.8</v>
       </c>
       <c r="G12" t="n">
-        <v>554</v>
+        <v>591</v>
       </c>
       <c r="H12" t="n">
-        <v>22.6</v>
+        <v>4.8</v>
       </c>
       <c r="I12" t="n">
-        <v>517</v>
+        <v>111</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>17.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>406</v>
       </c>
       <c r="L12" t="n">
-        <v>46.8</v>
+        <v>48.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1070</v>
+        <v>1107</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -3610,22 +3610,22 @@
         <v>5496</v>
       </c>
       <c r="F13" t="n">
-        <v>20.2</v>
+        <v>20.6</v>
       </c>
       <c r="G13" t="n">
-        <v>1521</v>
+        <v>1555</v>
       </c>
       <c r="H13" t="n">
-        <v>5.5</v>
+        <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>415</v>
+        <v>104</v>
       </c>
       <c r="J13" t="n">
-        <v>1.4</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>104</v>
+        <v>380</v>
       </c>
       <c r="L13" t="n">
         <v>27.1</v>
@@ -3654,34 +3654,34 @@
         <v>4602</v>
       </c>
       <c r="D14" t="n">
-        <v>62.7</v>
+        <v>58.7</v>
       </c>
       <c r="E14" t="n">
-        <v>2884</v>
+        <v>2700</v>
       </c>
       <c r="F14" t="n">
-        <v>25.3</v>
+        <v>26.7</v>
       </c>
       <c r="G14" t="n">
-        <v>1166</v>
+        <v>1227</v>
       </c>
       <c r="H14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>123</v>
+      </c>
+      <c r="J14" t="n">
         <v>12</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>552</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
-        <v>37.3</v>
+        <v>41.3</v>
       </c>
       <c r="M14" t="n">
-        <v>1718</v>
+        <v>1902</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -3716,16 +3716,16 @@
         <v>2111</v>
       </c>
       <c r="H15" t="n">
-        <v>31.8</v>
+        <v>4.5</v>
       </c>
       <c r="I15" t="n">
-        <v>1408</v>
+        <v>201</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>27.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1207</v>
       </c>
       <c r="L15" t="n">
         <v>79.5</v>
@@ -3735,7 +3735,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -3754,34 +3754,34 @@
         <v>372</v>
       </c>
       <c r="D16" t="n">
-        <v>47.5</v>
+        <v>46.5</v>
       </c>
       <c r="E16" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F16" t="n">
-        <v>29.7</v>
+        <v>25.7</v>
       </c>
       <c r="G16" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="H16" t="n">
-        <v>22.8</v>
+        <v>7.9</v>
       </c>
       <c r="I16" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>19.8</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="L16" t="n">
-        <v>52.5</v>
+        <v>53.5</v>
       </c>
       <c r="M16" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -3810,22 +3810,22 @@
         <v>56</v>
       </c>
       <c r="F17" t="n">
-        <v>27.8</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>7</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>36.1</v>
@@ -3854,38 +3854,38 @@
         <v>40</v>
       </c>
       <c r="D18" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="E18" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>20</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>8</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M18" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3904,34 +3904,34 @@
         <v>420</v>
       </c>
       <c r="D19" t="n">
-        <v>41.7</v>
+        <v>38.2</v>
       </c>
       <c r="E19" t="n">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>45.1</v>
+        <v>43.8</v>
       </c>
       <c r="G19" t="n">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H19" t="n">
-        <v>12.5</v>
+        <v>6.9</v>
       </c>
       <c r="I19" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>0.7</v>
+        <v>11.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="L19" t="n">
-        <v>58.3</v>
+        <v>61.8</v>
       </c>
       <c r="M19" t="n">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -3966,16 +3966,16 @@
         <v>131</v>
       </c>
       <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
         <v>2.9</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>11</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>37.1</v>
@@ -4016,16 +4016,16 @@
         <v>325</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>10.7</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>177</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>30.4</v>
@@ -4060,22 +4060,22 @@
         <v>227</v>
       </c>
       <c r="F22" t="n">
-        <v>41.7</v>
+        <v>36.1</v>
       </c>
       <c r="G22" t="n">
-        <v>227</v>
+        <v>197</v>
       </c>
       <c r="H22" t="n">
-        <v>16.7</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>13.9</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="L22" t="n">
         <v>58.3</v>
@@ -4085,7 +4085,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4110,22 +4110,22 @@
         <v>257</v>
       </c>
       <c r="F23" t="n">
-        <v>46.4</v>
+        <v>19.6</v>
       </c>
       <c r="G23" t="n">
-        <v>557</v>
+        <v>236</v>
       </c>
       <c r="H23" t="n">
-        <v>32.1</v>
+        <v>41.1</v>
       </c>
       <c r="I23" t="n">
-        <v>386</v>
+        <v>493</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="L23" t="n">
         <v>78.59999999999999</v>
@@ -4154,10 +4154,10 @@
         <v>2399</v>
       </c>
       <c r="D24" t="n">
-        <v>54.4</v>
+        <v>54</v>
       </c>
       <c r="E24" t="n">
-        <v>1306</v>
+        <v>1296</v>
       </c>
       <c r="F24" t="n">
         <v>29.5</v>
@@ -4166,22 +4166,22 @@
         <v>709</v>
       </c>
       <c r="H24" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I24" t="n">
-        <v>385</v>
+        <v>71</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="L24" t="n">
-        <v>45.6</v>
+        <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -4210,22 +4210,22 @@
         <v>505</v>
       </c>
       <c r="F25" t="n">
-        <v>26.8</v>
+        <v>24.7</v>
       </c>
       <c r="G25" t="n">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="H25" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" t="n">
         <v>5.2</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>38</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>32</v>
@@ -4260,22 +4260,22 @@
         <v>3628</v>
       </c>
       <c r="F26" t="n">
-        <v>28.7</v>
+        <v>19.3</v>
       </c>
       <c r="G26" t="n">
-        <v>1696</v>
+        <v>1144</v>
       </c>
       <c r="H26" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I26" t="n">
+        <v>552</v>
+      </c>
+      <c r="J26" t="n">
         <v>10</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>592</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>38.7</v>
@@ -4310,22 +4310,22 @@
         <v>80</v>
       </c>
       <c r="F27" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>361</v>
+        <v>200</v>
       </c>
       <c r="H27" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I27" t="n">
-        <v>561</v>
+        <v>241</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>481</v>
       </c>
       <c r="L27" t="n">
         <v>92</v>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4354,38 +4354,38 @@
         <v>5739</v>
       </c>
       <c r="D28" t="n">
-        <v>81.59999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>4682</v>
+        <v>4584</v>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>11.6</v>
       </c>
       <c r="G28" t="n">
-        <v>458</v>
+        <v>665</v>
       </c>
       <c r="H28" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>563</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0.6</v>
+        <v>8.5</v>
       </c>
       <c r="K28" t="n">
-        <v>35</v>
+        <v>490</v>
       </c>
       <c r="L28" t="n">
-        <v>18.4</v>
+        <v>20.1</v>
       </c>
       <c r="M28" t="n">
-        <v>1056</v>
+        <v>1155</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -4404,34 +4404,34 @@
         <v>1680</v>
       </c>
       <c r="D29" t="n">
-        <v>71.59999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F29" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="G29" t="n">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="H29" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>137</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="L29" t="n">
-        <v>28.4</v>
+        <v>28.8</v>
       </c>
       <c r="M29" t="n">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -4460,22 +4460,22 @@
         <v>98</v>
       </c>
       <c r="F30" t="n">
-        <v>46.3</v>
+        <v>48.8</v>
       </c>
       <c r="G30" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L30" t="n">
         <v>51.2</v>
@@ -4504,38 +4504,38 @@
         <v>3581</v>
       </c>
       <c r="D31" t="n">
-        <v>47.9</v>
+        <v>47.4</v>
       </c>
       <c r="E31" t="n">
-        <v>1714</v>
+        <v>1697</v>
       </c>
       <c r="F31" t="n">
-        <v>28.9</v>
+        <v>30.8</v>
       </c>
       <c r="G31" t="n">
-        <v>1035</v>
+        <v>1103</v>
       </c>
       <c r="H31" t="n">
-        <v>23.2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>832</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>21.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>781</v>
       </c>
       <c r="L31" t="n">
-        <v>52.1</v>
+        <v>52.6</v>
       </c>
       <c r="M31" t="n">
-        <v>1867</v>
+        <v>1884</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4554,34 +4554,34 @@
         <v>264</v>
       </c>
       <c r="D32" t="n">
-        <v>71.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="F32" t="n">
-        <v>25</v>
+        <v>31.2</v>
       </c>
       <c r="G32" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>3.1</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>8</v>
       </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
-        <v>28.1</v>
+        <v>34.4</v>
       </c>
       <c r="M32" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="N32" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         <v>21</v>
       </c>
       <c r="D33" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>78.90000000000001</v>
@@ -4616,26 +4616,26 @@
         <v>17</v>
       </c>
       <c r="H33" t="n">
-        <v>15.8</v>
+        <v>10.5</v>
       </c>
       <c r="I33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="M33" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4660,22 +4660,22 @@
         <v>600</v>
       </c>
       <c r="F34" t="n">
-        <v>11.5</v>
+        <v>7.7</v>
       </c>
       <c r="G34" t="n">
-        <v>95</v>
+        <v>63</v>
       </c>
       <c r="H34" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="I34" t="n">
+        <v>32</v>
+      </c>
+      <c r="J34" t="n">
         <v>15.4</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>126</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>26.9</v>
@@ -4704,38 +4704,38 @@
         <v>1875</v>
       </c>
       <c r="D35" t="n">
-        <v>40.5</v>
+        <v>37.9</v>
       </c>
       <c r="E35" t="n">
-        <v>760</v>
+        <v>712</v>
       </c>
       <c r="F35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G35" t="n">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="H35" t="n">
-        <v>37.4</v>
+        <v>5.6</v>
       </c>
       <c r="I35" t="n">
-        <v>702</v>
+        <v>106</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>36.4</v>
       </c>
       <c r="K35" t="n">
-        <v>19</v>
+        <v>683</v>
       </c>
       <c r="L35" t="n">
-        <v>59.5</v>
+        <v>62.1</v>
       </c>
       <c r="M35" t="n">
-        <v>1115</v>
+        <v>1163</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4760,22 +4760,22 @@
         <v>864</v>
       </c>
       <c r="F36" t="n">
-        <v>16.9</v>
+        <v>11.3</v>
       </c>
       <c r="G36" t="n">
-        <v>203</v>
+        <v>136</v>
       </c>
       <c r="H36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>68</v>
+      </c>
+      <c r="J36" t="n">
         <v>11.3</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>136</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>28.2</v>
@@ -4804,38 +4804,38 @@
         <v>1021</v>
       </c>
       <c r="D37" t="n">
-        <v>35.2</v>
+        <v>33</v>
       </c>
       <c r="E37" t="n">
-        <v>360</v>
+        <v>336</v>
       </c>
       <c r="F37" t="n">
-        <v>13.6</v>
+        <v>19.3</v>
       </c>
       <c r="G37" t="n">
-        <v>139</v>
+        <v>197</v>
       </c>
       <c r="H37" t="n">
-        <v>50</v>
+        <v>1.1</v>
       </c>
       <c r="I37" t="n">
-        <v>511</v>
+        <v>12</v>
       </c>
       <c r="J37" t="n">
-        <v>1.1</v>
+        <v>46.6</v>
       </c>
       <c r="K37" t="n">
-        <v>12</v>
+        <v>476</v>
       </c>
       <c r="L37" t="n">
-        <v>64.8</v>
+        <v>67</v>
       </c>
       <c r="M37" t="n">
-        <v>661</v>
+        <v>685</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4860,22 +4860,22 @@
         <v>2164</v>
       </c>
       <c r="F38" t="n">
-        <v>33.2</v>
+        <v>30</v>
       </c>
       <c r="G38" t="n">
-        <v>1458</v>
+        <v>1317</v>
       </c>
       <c r="H38" t="n">
-        <v>17.1</v>
+        <v>7.5</v>
       </c>
       <c r="I38" t="n">
-        <v>753</v>
+        <v>329</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4</v>
+        <v>13.2</v>
       </c>
       <c r="K38" t="n">
-        <v>16</v>
+        <v>580</v>
       </c>
       <c r="L38" t="n">
         <v>50.7</v>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -4916,16 +4916,16 @@
         <v>162</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
         <v>50</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>162</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
       </c>
       <c r="L39" t="n">
         <v>100</v>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -4960,22 +4960,22 @@
         <v>68</v>
       </c>
       <c r="F40" t="n">
-        <v>21.7</v>
+        <v>19.6</v>
       </c>
       <c r="G40" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H40" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I40" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" t="n">
         <v>28.3</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>39</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>50</v>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5016,16 +5016,16 @@
         <v>12</v>
       </c>
       <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
         <v>53.1</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>105</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
       </c>
       <c r="L41" t="n">
         <v>59.2</v>
@@ -5035,7 +5035,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5066,16 +5066,16 @@
         <v>60</v>
       </c>
       <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
         <v>14.8</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>45</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>34.4</v>
@@ -5110,22 +5110,22 @@
         <v>875</v>
       </c>
       <c r="F43" t="n">
-        <v>23.1</v>
+        <v>20.2</v>
       </c>
       <c r="G43" t="n">
-        <v>318</v>
+        <v>278</v>
       </c>
       <c r="H43" t="n">
-        <v>13.3</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>183</v>
+        <v>56</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L43" t="n">
         <v>36.4</v>
@@ -5160,22 +5160,22 @@
         <v>734</v>
       </c>
       <c r="F44" t="n">
-        <v>37.3</v>
+        <v>28</v>
       </c>
       <c r="G44" t="n">
-        <v>501</v>
+        <v>376</v>
       </c>
       <c r="H44" t="n">
-        <v>8</v>
+        <v>10.7</v>
       </c>
       <c r="I44" t="n">
-        <v>107</v>
+        <v>143</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L44" t="n">
         <v>45.3</v>
@@ -5260,13 +5260,13 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>44.4</v>
+        <v>33.3</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>5.6</v>
+        <v>16.7</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -5304,34 +5304,34 @@
         <v>15387</v>
       </c>
       <c r="D47" t="n">
-        <v>77.5</v>
+        <v>62</v>
       </c>
       <c r="E47" t="n">
-        <v>11919</v>
+        <v>9536</v>
       </c>
       <c r="F47" t="n">
-        <v>16.2</v>
+        <v>29.6</v>
       </c>
       <c r="G47" t="n">
-        <v>2492</v>
+        <v>4551</v>
       </c>
       <c r="H47" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I47" t="n">
+        <v>325</v>
+      </c>
+      <c r="J47" t="n">
         <v>6.3</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>975</v>
       </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
-        <v>22.5</v>
+        <v>38</v>
       </c>
       <c r="M47" t="n">
-        <v>3467</v>
+        <v>5851</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -5440,7 +5440,7 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -5452,26 +5452,26 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>47.5</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>45.9</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>90.2</v>
+        <v>91.8</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -5490,34 +5490,34 @@
         <v>1468</v>
       </c>
       <c r="D3" t="n">
-        <v>61.3</v>
+        <v>57.2</v>
       </c>
       <c r="E3" t="n">
-        <v>900</v>
+        <v>840</v>
       </c>
       <c r="F3" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="G3" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="H3" t="n">
-        <v>25.4</v>
+        <v>11</v>
       </c>
       <c r="I3" t="n">
-        <v>373</v>
+        <v>161</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>238</v>
       </c>
       <c r="L3" t="n">
-        <v>38.7</v>
+        <v>42.8</v>
       </c>
       <c r="M3" t="n">
-        <v>569</v>
+        <v>628</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -5540,34 +5540,34 @@
         <v>669</v>
       </c>
       <c r="D4" t="n">
-        <v>57.4</v>
+        <v>55</v>
       </c>
       <c r="E4" t="n">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="F4" t="n">
-        <v>17.2</v>
+        <v>20.1</v>
       </c>
       <c r="G4" t="n">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="H4" t="n">
-        <v>24.9</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>19.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="L4" t="n">
-        <v>42.6</v>
+        <v>45</v>
       </c>
       <c r="M4" t="n">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -5602,16 +5602,16 @@
         <v>105</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>15.8</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>35</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>63.2</v>
@@ -5640,34 +5640,34 @@
         <v>368</v>
       </c>
       <c r="D6" t="n">
-        <v>36.4</v>
+        <v>31.8</v>
       </c>
       <c r="E6" t="n">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="F6" t="n">
-        <v>57.6</v>
+        <v>62.1</v>
       </c>
       <c r="G6" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="H6" t="n">
-        <v>6.1</v>
+        <v>1.5</v>
       </c>
       <c r="I6" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L6" t="n">
-        <v>63.6</v>
+        <v>68.2</v>
       </c>
       <c r="M6" t="n">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -5690,34 +5690,34 @@
         <v>717</v>
       </c>
       <c r="D7" t="n">
-        <v>63.9</v>
+        <v>60.2</v>
       </c>
       <c r="E7" t="n">
-        <v>458</v>
+        <v>432</v>
       </c>
       <c r="F7" t="n">
-        <v>28.5</v>
+        <v>29.3</v>
       </c>
       <c r="G7" t="n">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="H7" t="n">
-        <v>7.2</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="L7" t="n">
-        <v>36.1</v>
+        <v>39.8</v>
       </c>
       <c r="M7" t="n">
-        <v>259</v>
+        <v>285</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -5746,22 +5746,22 @@
         <v>315</v>
       </c>
       <c r="F8" t="n">
-        <v>31.3</v>
+        <v>34.3</v>
       </c>
       <c r="G8" t="n">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="H8" t="n">
-        <v>22.4</v>
+        <v>1.5</v>
       </c>
       <c r="I8" t="n">
-        <v>153</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>17.9</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="L8" t="n">
         <v>53.7</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -5790,34 +5790,34 @@
         <v>1731</v>
       </c>
       <c r="D9" t="n">
-        <v>77.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1342</v>
+        <v>1326</v>
       </c>
       <c r="F9" t="n">
-        <v>14.7</v>
+        <v>16.1</v>
       </c>
       <c r="G9" t="n">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="H9" t="n">
-        <v>6.9</v>
+        <v>1.8</v>
       </c>
       <c r="I9" t="n">
-        <v>119</v>
+        <v>32</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9</v>
+        <v>5.5</v>
       </c>
       <c r="K9" t="n">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="L9" t="n">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="M9" t="n">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -5840,34 +5840,34 @@
         <v>533</v>
       </c>
       <c r="D10" t="n">
-        <v>59.7</v>
+        <v>58.4</v>
       </c>
       <c r="E10" t="n">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="F10" t="n">
-        <v>20.8</v>
+        <v>23.4</v>
       </c>
       <c r="G10" t="n">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
         <v>18.2</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>97</v>
       </c>
-      <c r="J10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>7</v>
-      </c>
       <c r="L10" t="n">
-        <v>40.3</v>
+        <v>41.6</v>
       </c>
       <c r="M10" t="n">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -5902,16 +5902,16 @@
         <v>31</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>18.8</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>17</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>53.1</v>
@@ -5946,22 +5946,22 @@
         <v>296</v>
       </c>
       <c r="F12" t="n">
-        <v>42.7</v>
+        <v>38.2</v>
       </c>
       <c r="G12" t="n">
-        <v>313</v>
+        <v>280</v>
       </c>
       <c r="H12" t="n">
-        <v>16.9</v>
+        <v>5.6</v>
       </c>
       <c r="I12" t="n">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>15.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="L12" t="n">
         <v>59.6</v>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5990,34 +5990,34 @@
         <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>51.4</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>37.5</v>
+        <v>45.1</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>10.4</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>9.5</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>48.6</v>
+        <v>58</v>
       </c>
       <c r="M13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -6052,13 +6052,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>33.3</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -6071,7 +6071,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6146,22 +6146,22 @@
         <v>42</v>
       </c>
       <c r="F16" t="n">
-        <v>54.3</v>
+        <v>51.4</v>
       </c>
       <c r="G16" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>57.1</v>
@@ -6190,16 +6190,16 @@
         <v>13</v>
       </c>
       <c r="D17" t="n">
-        <v>64.3</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>35.7</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -6214,10 +6214,10 @@
         <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>35.7</v>
+        <v>50</v>
       </c>
       <c r="M17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -6240,34 +6240,34 @@
         <v>239</v>
       </c>
       <c r="D18" t="n">
-        <v>71.59999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F18" t="n">
-        <v>20.6</v>
+        <v>23.5</v>
       </c>
       <c r="G18" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H18" t="n">
-        <v>7.8</v>
+        <v>2.9</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L18" t="n">
-        <v>28.4</v>
+        <v>29.4</v>
       </c>
       <c r="M18" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -6296,22 +6296,22 @@
         <v>237</v>
       </c>
       <c r="F19" t="n">
-        <v>22.9</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3</v>
+      </c>
+      <c r="J19" t="n">
         <v>14.7</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>56</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>37.6</v>
@@ -6346,22 +6346,22 @@
         <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>53.2</v>
+        <v>48.4</v>
       </c>
       <c r="G20" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="H20" t="n">
-        <v>19.4</v>
+        <v>14.5</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6</v>
+        <v>11.3</v>
       </c>
       <c r="K20" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
         <v>74.2</v>
@@ -6390,38 +6390,38 @@
         <v>152</v>
       </c>
       <c r="D21" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="E21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>44.6</v>
+        <v>33.8</v>
       </c>
       <c r="G21" t="n">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H21" t="n">
-        <v>35.4</v>
+        <v>26.2</v>
       </c>
       <c r="I21" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>21.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L21" t="n">
-        <v>80</v>
+        <v>81.5</v>
       </c>
       <c r="M21" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6440,34 +6440,34 @@
         <v>467</v>
       </c>
       <c r="D22" t="n">
-        <v>64.2</v>
+        <v>63.6</v>
       </c>
       <c r="E22" t="n">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>21.2</v>
       </c>
       <c r="G22" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="H22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" t="n">
         <v>12.7</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>59</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
-        <v>35.8</v>
+        <v>36.4</v>
       </c>
       <c r="M22" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -6490,31 +6490,31 @@
         <v>96</v>
       </c>
       <c r="D23" t="n">
-        <v>71</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F23" t="n">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="G23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H23" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
         <v>10.1</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>10</v>
       </c>
-      <c r="J23" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K23" t="n">
-        <v>1</v>
-      </c>
       <c r="L23" t="n">
-        <v>29</v>
+        <v>29.6</v>
       </c>
       <c r="M23" t="n">
         <v>28</v>
@@ -6540,34 +6540,34 @@
         <v>1808</v>
       </c>
       <c r="D24" t="n">
-        <v>89.09999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>1612</v>
+        <v>1598</v>
       </c>
       <c r="F24" t="n">
-        <v>8.5</v>
+        <v>7.8</v>
       </c>
       <c r="G24" t="n">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="H24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>28</v>
+      </c>
+      <c r="J24" t="n">
         <v>2.3</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>42</v>
       </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
-        <v>10.9</v>
+        <v>11.6</v>
       </c>
       <c r="M24" t="n">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -6596,19 +6596,19 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>37</v>
+        <v>22.2</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>37</v>
+        <v>22.2</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>29.6</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6652,13 +6652,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
         <v>2.7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -6690,34 +6690,34 @@
         <v>1312</v>
       </c>
       <c r="D27" t="n">
-        <v>67.5</v>
+        <v>66.8</v>
       </c>
       <c r="E27" t="n">
-        <v>886</v>
+        <v>876</v>
       </c>
       <c r="F27" t="n">
-        <v>25.5</v>
+        <v>26.3</v>
       </c>
       <c r="G27" t="n">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="H27" t="n">
-        <v>6.9</v>
+        <v>0.4</v>
       </c>
       <c r="I27" t="n">
-        <v>91</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="L27" t="n">
-        <v>32.5</v>
+        <v>33.2</v>
       </c>
       <c r="M27" t="n">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -6746,22 +6746,22 @@
         <v>139</v>
       </c>
       <c r="F28" t="n">
-        <v>31.6</v>
+        <v>28.9</v>
       </c>
       <c r="G28" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H28" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="I28" t="n">
+        <v>6</v>
+      </c>
+      <c r="J28" t="n">
         <v>7.9</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>18</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>39.5</v>
@@ -6790,34 +6790,34 @@
         <v>1923</v>
       </c>
       <c r="D29" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="E29" t="n">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="F29" t="n">
-        <v>27.1</v>
+        <v>30.8</v>
       </c>
       <c r="G29" t="n">
-        <v>521</v>
+        <v>592</v>
       </c>
       <c r="H29" t="n">
-        <v>24.2</v>
+        <v>1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>466</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="L29" t="n">
-        <v>51.3</v>
+        <v>51.6</v>
       </c>
       <c r="M29" t="n">
-        <v>987</v>
+        <v>992</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -6852,16 +6852,16 @@
         <v>92</v>
       </c>
       <c r="H30" t="n">
-        <v>22.2</v>
+        <v>1.9</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>20.4</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
         <v>100</v>
@@ -6871,7 +6871,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6896,19 +6896,19 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>47.4</v>
+        <v>26.3</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
         <v>31.6</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>0</v>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -6952,16 +6952,16 @@
         <v>93</v>
       </c>
       <c r="H32" t="n">
-        <v>19.7</v>
+        <v>2.6</v>
       </c>
       <c r="I32" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="J32" t="n">
-        <v>1.7</v>
+        <v>18.8</v>
       </c>
       <c r="K32" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="L32" t="n">
         <v>41</v>
@@ -6996,22 +6996,22 @@
         <v>14</v>
       </c>
       <c r="F33" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="G33" t="n">
+        <v>13</v>
+      </c>
+      <c r="H33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" t="n">
         <v>32.1</v>
       </c>
-      <c r="G33" t="n">
+      <c r="K33" t="n">
         <v>14</v>
-      </c>
-      <c r="H33" t="n">
-        <v>35.7</v>
-      </c>
-      <c r="I33" t="n">
-        <v>16</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>67.90000000000001</v>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7046,16 +7046,16 @@
         <v>258</v>
       </c>
       <c r="F34" t="n">
-        <v>21.9</v>
+        <v>19.3</v>
       </c>
       <c r="G34" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="H34" t="n">
-        <v>1.8</v>
+        <v>4.4</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -7090,34 +7090,34 @@
         <v>346</v>
       </c>
       <c r="D35" t="n">
+        <v>48.2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>30.6</v>
+      </c>
+      <c r="G35" t="n">
+        <v>106</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>20</v>
+      </c>
+      <c r="K35" t="n">
+        <v>69</v>
+      </c>
+      <c r="L35" t="n">
         <v>51.8</v>
       </c>
-      <c r="E35" t="n">
+      <c r="M35" t="n">
         <v>179</v>
-      </c>
-      <c r="F35" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="G35" t="n">
-        <v>94</v>
-      </c>
-      <c r="H35" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="I35" t="n">
-        <v>73</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>167</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -7146,19 +7146,19 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>23.1</v>
+        <v>19.2</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>17.3</v>
+        <v>5.8</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7190,38 +7190,38 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>46.8</v>
+        <v>42.9</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>31.2</v>
+        <v>35.1</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
         <v>22.1</v>
       </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
       <c r="K37" t="n">
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>53.2</v>
+        <v>57.1</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7252,16 +7252,16 @@
         <v>60</v>
       </c>
       <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
         <v>4.5</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>11</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>29.5</v>
@@ -7290,34 +7290,34 @@
         <v>180</v>
       </c>
       <c r="D39" t="n">
-        <v>32.2</v>
+        <v>31.1</v>
       </c>
       <c r="E39" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F39" t="n">
-        <v>46.3</v>
+        <v>40.7</v>
       </c>
       <c r="G39" t="n">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="H39" t="n">
-        <v>21.5</v>
+        <v>11.9</v>
       </c>
       <c r="I39" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>16.4</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
-        <v>67.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -7346,22 +7346,22 @@
         <v>199</v>
       </c>
       <c r="F40" t="n">
-        <v>26.7</v>
+        <v>33.3</v>
       </c>
       <c r="G40" t="n">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="H40" t="n">
-        <v>15.6</v>
+        <v>2.2</v>
       </c>
       <c r="I40" t="n">
-        <v>58</v>
+        <v>8</v>
       </c>
       <c r="J40" t="n">
-        <v>4.4</v>
+        <v>11.1</v>
       </c>
       <c r="K40" t="n">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="L40" t="n">
         <v>46.7</v>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -7390,34 +7390,34 @@
         <v>1553</v>
       </c>
       <c r="D41" t="n">
-        <v>64.59999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="E41" t="n">
-        <v>1003</v>
+        <v>987</v>
       </c>
       <c r="F41" t="n">
-        <v>30.2</v>
+        <v>27.1</v>
       </c>
       <c r="G41" t="n">
-        <v>469</v>
+        <v>421</v>
       </c>
       <c r="H41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I41" t="n">
+        <v>65</v>
+      </c>
+      <c r="J41" t="n">
         <v>5.2</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>81</v>
       </c>
-      <c r="J41" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
-        <v>35.4</v>
+        <v>36.5</v>
       </c>
       <c r="M41" t="n">
-        <v>550</v>
+        <v>566</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -7446,22 +7446,22 @@
         <v>219</v>
       </c>
       <c r="F42" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="G42" t="n">
+        <v>90</v>
+      </c>
+      <c r="H42" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I42" t="n">
         <v>30</v>
       </c>
-      <c r="G42" t="n">
-        <v>120</v>
-      </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>15</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>60</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>45</v>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7496,22 +7496,22 @@
         <v>5</v>
       </c>
       <c r="F43" t="n">
-        <v>65.8</v>
+        <v>39.5</v>
       </c>
       <c r="G43" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H43" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" t="n">
         <v>10.5</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>2</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>76.3</v>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7546,22 +7546,22 @@
         <v>304</v>
       </c>
       <c r="F44" t="n">
-        <v>52.6</v>
+        <v>40.2</v>
       </c>
       <c r="G44" t="n">
-        <v>1109</v>
+        <v>848</v>
       </c>
       <c r="H44" t="n">
-        <v>33</v>
+        <v>13.4</v>
       </c>
       <c r="I44" t="n">
-        <v>696</v>
+        <v>283</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>674</v>
       </c>
       <c r="L44" t="n">
         <v>85.59999999999999</v>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7596,22 +7596,22 @@
         <v>234</v>
       </c>
       <c r="F45" t="n">
-        <v>42.3</v>
+        <v>25.4</v>
       </c>
       <c r="G45" t="n">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="H45" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="I45" t="n">
+        <v>101</v>
+      </c>
+      <c r="J45" t="n">
         <v>14.1</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>78</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="K45" t="n">
-        <v>8</v>
       </c>
       <c r="L45" t="n">
         <v>57.7</v>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7640,34 +7640,34 @@
         <v>1417</v>
       </c>
       <c r="D46" t="n">
-        <v>73.90000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="E46" t="n">
-        <v>1047</v>
+        <v>900</v>
       </c>
       <c r="F46" t="n">
-        <v>14.8</v>
+        <v>24.2</v>
       </c>
       <c r="G46" t="n">
-        <v>209</v>
+        <v>343</v>
       </c>
       <c r="H46" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I46" t="n">
+        <v>18</v>
+      </c>
+      <c r="J46" t="n">
         <v>11</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>156</v>
       </c>
-      <c r="J46" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K46" t="n">
-        <v>4</v>
-      </c>
       <c r="L46" t="n">
-        <v>26.1</v>
+        <v>36.5</v>
       </c>
       <c r="M46" t="n">
-        <v>370</v>
+        <v>517</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -7776,38 +7776,38 @@
         <v>394</v>
       </c>
       <c r="D2" t="n">
-        <v>59.5</v>
+        <v>58.8</v>
       </c>
       <c r="E2" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F2" t="n">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H2" t="n">
-        <v>28.6</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
-        <v>112</v>
+        <v>16</v>
       </c>
       <c r="J2" t="n">
-        <v>0.3</v>
+        <v>25.9</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>102</v>
       </c>
       <c r="L2" t="n">
-        <v>40.5</v>
+        <v>41.2</v>
       </c>
       <c r="M2" t="n">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7832,22 +7832,22 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>27.5</v>
+        <v>25.5</v>
       </c>
       <c r="G3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="n">
         <v>52.9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>121</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4</v>
       </c>
       <c r="L3" t="n">
         <v>82.40000000000001</v>
@@ -7857,7 +7857,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7876,34 +7876,34 @@
         <v>1640</v>
       </c>
       <c r="D4" t="n">
-        <v>65.90000000000001</v>
+        <v>65</v>
       </c>
       <c r="E4" t="n">
-        <v>1080</v>
+        <v>1067</v>
       </c>
       <c r="F4" t="n">
-        <v>17.1</v>
+        <v>17.9</v>
       </c>
       <c r="G4" t="n">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="H4" t="n">
-        <v>17.1</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>280</v>
+        <v>27</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>15.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>253</v>
       </c>
       <c r="L4" t="n">
-        <v>34.1</v>
+        <v>35</v>
       </c>
       <c r="M4" t="n">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -7926,38 +7926,38 @@
         <v>144</v>
       </c>
       <c r="D5" t="n">
-        <v>47.8</v>
+        <v>40.6</v>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>25</v>
+      </c>
+      <c r="H5" t="n">
         <v>15.9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>23</v>
       </c>
-      <c r="H5" t="n">
-        <v>34.8</v>
-      </c>
-      <c r="I5" t="n">
-        <v>50</v>
-      </c>
       <c r="J5" t="n">
-        <v>1.4</v>
+        <v>26.1</v>
       </c>
       <c r="K5" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="L5" t="n">
-        <v>52.2</v>
+        <v>59.4</v>
       </c>
       <c r="M5" t="n">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -7982,22 +7982,22 @@
         <v>147</v>
       </c>
       <c r="F6" t="n">
-        <v>40.6</v>
+        <v>34.4</v>
       </c>
       <c r="G6" t="n">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="H6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" t="n">
         <v>21.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>86</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>62.5</v>
@@ -8007,7 +8007,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8026,34 +8026,34 @@
         <v>2200</v>
       </c>
       <c r="D7" t="n">
-        <v>66.2</v>
+        <v>60.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1456</v>
+        <v>1329</v>
       </c>
       <c r="F7" t="n">
-        <v>16.9</v>
+        <v>22.7</v>
       </c>
       <c r="G7" t="n">
-        <v>372</v>
+        <v>499</v>
       </c>
       <c r="H7" t="n">
-        <v>16.5</v>
+        <v>5.4</v>
       </c>
       <c r="I7" t="n">
-        <v>364</v>
+        <v>118</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>11.5</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>254</v>
       </c>
       <c r="L7" t="n">
-        <v>33.8</v>
+        <v>39.6</v>
       </c>
       <c r="M7" t="n">
-        <v>745</v>
+        <v>872</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -8076,34 +8076,34 @@
         <v>2694</v>
       </c>
       <c r="D8" t="n">
-        <v>59.4</v>
+        <v>58.6</v>
       </c>
       <c r="E8" t="n">
-        <v>1600</v>
+        <v>1580</v>
       </c>
       <c r="F8" t="n">
-        <v>28.9</v>
+        <v>28.6</v>
       </c>
       <c r="G8" t="n">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="H8" t="n">
-        <v>10.2</v>
+        <v>3.4</v>
       </c>
       <c r="I8" t="n">
-        <v>273</v>
+        <v>91</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5</v>
+        <v>9.4</v>
       </c>
       <c r="K8" t="n">
-        <v>41</v>
+        <v>253</v>
       </c>
       <c r="L8" t="n">
-        <v>40.6</v>
+        <v>41.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1094</v>
+        <v>1114</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -8138,16 +8138,16 @@
         <v>172</v>
       </c>
       <c r="H9" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>34</v>
+      </c>
+      <c r="J9" t="n">
         <v>26.7</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>207</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>34</v>
       </c>
       <c r="L9" t="n">
         <v>53.3</v>
@@ -8157,7 +8157,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8182,22 +8182,22 @@
         <v>38</v>
       </c>
       <c r="F10" t="n">
-        <v>18.5</v>
+        <v>22.8</v>
       </c>
       <c r="G10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H10" t="n">
-        <v>10.9</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.1</v>
+        <v>7.6</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>30.4</v>
@@ -8232,22 +8232,22 @@
         <v>1856</v>
       </c>
       <c r="F11" t="n">
-        <v>8.1</v>
+        <v>8.9</v>
       </c>
       <c r="G11" t="n">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="H11" t="n">
-        <v>12.2</v>
+        <v>0.3</v>
       </c>
       <c r="I11" t="n">
-        <v>288</v>
+        <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8</v>
+        <v>12</v>
       </c>
       <c r="K11" t="n">
-        <v>18</v>
+        <v>282</v>
       </c>
       <c r="L11" t="n">
         <v>21.1</v>
@@ -8276,38 +8276,38 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>27.1</v>
+        <v>9.5</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>35.2</v>
+        <v>20.1</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>33.5</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>62.7</v>
+        <v>63</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8326,34 +8326,34 @@
         <v>3469</v>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>57.6</v>
       </c>
       <c r="E13" t="n">
-        <v>2011</v>
+        <v>1998</v>
       </c>
       <c r="F13" t="n">
-        <v>18.1</v>
+        <v>21.7</v>
       </c>
       <c r="G13" t="n">
-        <v>628</v>
+        <v>754</v>
       </c>
       <c r="H13" t="n">
-        <v>21.4</v>
+        <v>1.4</v>
       </c>
       <c r="I13" t="n">
-        <v>742</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>2.5</v>
+        <v>19.2</v>
       </c>
       <c r="K13" t="n">
-        <v>88</v>
+        <v>666</v>
       </c>
       <c r="L13" t="n">
-        <v>42</v>
+        <v>42.4</v>
       </c>
       <c r="M13" t="n">
-        <v>1458</v>
+        <v>1470</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -8376,38 +8376,38 @@
         <v>727</v>
       </c>
       <c r="D14" t="n">
-        <v>53.7</v>
+        <v>52.9</v>
       </c>
       <c r="E14" t="n">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="F14" t="n">
-        <v>26.4</v>
+        <v>25.6</v>
       </c>
       <c r="G14" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H14" t="n">
-        <v>19.8</v>
+        <v>7.4</v>
       </c>
       <c r="I14" t="n">
-        <v>144</v>
+        <v>54</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>102</v>
       </c>
       <c r="L14" t="n">
-        <v>46.3</v>
+        <v>47.1</v>
       </c>
       <c r="M14" t="n">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8426,34 +8426,34 @@
         <v>1098</v>
       </c>
       <c r="D15" t="n">
-        <v>53.7</v>
+        <v>50</v>
       </c>
       <c r="E15" t="n">
-        <v>590</v>
+        <v>549</v>
       </c>
       <c r="F15" t="n">
-        <v>23.1</v>
+        <v>26.1</v>
       </c>
       <c r="G15" t="n">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="H15" t="n">
-        <v>23.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>254</v>
+        <v>106</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>14.2</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="L15" t="n">
-        <v>46.3</v>
+        <v>50</v>
       </c>
       <c r="M15" t="n">
-        <v>508</v>
+        <v>549</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -8482,22 +8482,22 @@
         <v>1833</v>
       </c>
       <c r="F16" t="n">
-        <v>34.9</v>
+        <v>36</v>
       </c>
       <c r="G16" t="n">
-        <v>1195</v>
+        <v>1235</v>
       </c>
       <c r="H16" t="n">
-        <v>11.6</v>
+        <v>1.2</v>
       </c>
       <c r="I16" t="n">
-        <v>398</v>
+        <v>40</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="L16" t="n">
         <v>46.5</v>
@@ -8532,22 +8532,22 @@
         <v>166</v>
       </c>
       <c r="F17" t="n">
-        <v>21.7</v>
+        <v>10</v>
       </c>
       <c r="G17" t="n">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="H17" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>45</v>
+      </c>
+      <c r="J17" t="n">
         <v>35</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>134</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>56.7</v>
@@ -8557,7 +8557,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -8576,34 +8576,34 @@
         <v>241</v>
       </c>
       <c r="D18" t="n">
-        <v>67.09999999999999</v>
+        <v>59.5</v>
       </c>
       <c r="E18" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="F18" t="n">
-        <v>17.9</v>
+        <v>25.4</v>
       </c>
       <c r="G18" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="n">
         <v>15.1</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>36</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
-        <v>32.9</v>
+        <v>40.5</v>
       </c>
       <c r="M18" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>

--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_pop_step1_Central_African_Republic___CAR_1008_03PM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_pop_step1_Central_African_Republic___CAR_1008_03PM.xlsx
@@ -524,16 +524,16 @@
         <v>172</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>45.5</v>
       </c>
       <c r="G2" t="n">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="H2" t="n">
-        <v>6.3</v>
+        <v>10.7</v>
       </c>
       <c r="I2" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="J2" t="n">
         <v>14.7</v>
@@ -574,16 +574,16 @@
         <v>1300</v>
       </c>
       <c r="F3" t="n">
-        <v>29.3</v>
+        <v>26.2</v>
       </c>
       <c r="G3" t="n">
-        <v>626</v>
+        <v>560</v>
       </c>
       <c r="H3" t="n">
-        <v>4</v>
+        <v>7.1</v>
       </c>
       <c r="I3" t="n">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="J3" t="n">
         <v>5.8</v>
@@ -624,16 +624,16 @@
         <v>1875</v>
       </c>
       <c r="F4" t="n">
-        <v>28.1</v>
+        <v>25.3</v>
       </c>
       <c r="G4" t="n">
-        <v>830</v>
+        <v>750</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
         <v>8.6</v>
@@ -674,16 +674,16 @@
         <v>81</v>
       </c>
       <c r="F5" t="n">
-        <v>40.4</v>
+        <v>32.3</v>
       </c>
       <c r="G5" t="n">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>11.7</v>
       </c>
       <c r="I5" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="J5" t="n">
         <v>35.9</v>
@@ -724,16 +724,16 @@
         <v>2018</v>
       </c>
       <c r="F6" t="n">
-        <v>17.6</v>
+        <v>13.4</v>
       </c>
       <c r="G6" t="n">
-        <v>678</v>
+        <v>516</v>
       </c>
       <c r="H6" t="n">
-        <v>10.9</v>
+        <v>15.1</v>
       </c>
       <c r="I6" t="n">
-        <v>420</v>
+        <v>581</v>
       </c>
       <c r="J6" t="n">
         <v>19.2</v>
@@ -774,16 +774,16 @@
         <v>2346</v>
       </c>
       <c r="F7" t="n">
-        <v>16.2</v>
+        <v>12.7</v>
       </c>
       <c r="G7" t="n">
-        <v>584</v>
+        <v>455</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>8.1</v>
       </c>
       <c r="I7" t="n">
-        <v>163</v>
+        <v>292</v>
       </c>
       <c r="J7" t="n">
         <v>14</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -824,16 +824,16 @@
         <v>145</v>
       </c>
       <c r="F8" t="n">
-        <v>38.7</v>
+        <v>18.1</v>
       </c>
       <c r="G8" t="n">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="H8" t="n">
-        <v>9.699999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="I8" t="n">
-        <v>43</v>
+        <v>133</v>
       </c>
       <c r="J8" t="n">
         <v>18.7</v>
@@ -874,16 +874,16 @@
         <v>537</v>
       </c>
       <c r="F9" t="n">
-        <v>33.9</v>
+        <v>12.2</v>
       </c>
       <c r="G9" t="n">
-        <v>431</v>
+        <v>156</v>
       </c>
       <c r="H9" t="n">
-        <v>10.6</v>
+        <v>32.2</v>
       </c>
       <c r="I9" t="n">
-        <v>134</v>
+        <v>410</v>
       </c>
       <c r="J9" t="n">
         <v>13.3</v>
@@ -924,16 +924,16 @@
         <v>2191</v>
       </c>
       <c r="F10" t="n">
-        <v>53.7</v>
+        <v>48.5</v>
       </c>
       <c r="G10" t="n">
-        <v>3327</v>
+        <v>3002</v>
       </c>
       <c r="H10" t="n">
-        <v>7.9</v>
+        <v>13.1</v>
       </c>
       <c r="I10" t="n">
-        <v>487</v>
+        <v>811</v>
       </c>
       <c r="J10" t="n">
         <v>3.1</v>
@@ -974,16 +974,16 @@
         <v>1316</v>
       </c>
       <c r="F11" t="n">
-        <v>37.7</v>
+        <v>34.5</v>
       </c>
       <c r="G11" t="n">
-        <v>1149</v>
+        <v>1051</v>
       </c>
       <c r="H11" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="I11" t="n">
-        <v>157</v>
+        <v>255</v>
       </c>
       <c r="J11" t="n">
         <v>13.9</v>
@@ -999,7 +999,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1024,16 +1024,16 @@
         <v>1214</v>
       </c>
       <c r="F12" t="n">
-        <v>35.9</v>
+        <v>29.6</v>
       </c>
       <c r="G12" t="n">
-        <v>741</v>
+        <v>611</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9</v>
+        <v>8.1</v>
       </c>
       <c r="I12" t="n">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="J12" t="n">
         <v>3.3</v>
@@ -1074,16 +1074,16 @@
         <v>1070</v>
       </c>
       <c r="F13" t="n">
-        <v>33.9</v>
+        <v>31.5</v>
       </c>
       <c r="G13" t="n">
-        <v>704</v>
+        <v>654</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="I13" t="n">
-        <v>57</v>
+        <v>108</v>
       </c>
       <c r="J13" t="n">
         <v>11.8</v>
@@ -1124,16 +1124,16 @@
         <v>6214</v>
       </c>
       <c r="F14" t="n">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="G14" t="n">
-        <v>1931</v>
+        <v>1889</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="I14" t="n">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="J14" t="n">
         <v>10.8</v>
@@ -1174,16 +1174,16 @@
         <v>2366</v>
       </c>
       <c r="F15" t="n">
-        <v>23.2</v>
+        <v>13.8</v>
       </c>
       <c r="G15" t="n">
-        <v>1142</v>
+        <v>680</v>
       </c>
       <c r="H15" t="n">
-        <v>8.300000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="I15" t="n">
-        <v>408</v>
+        <v>870</v>
       </c>
       <c r="J15" t="n">
         <v>20.4</v>
@@ -1224,16 +1224,16 @@
         <v>1464</v>
       </c>
       <c r="F16" t="n">
-        <v>39.4</v>
+        <v>27.5</v>
       </c>
       <c r="G16" t="n">
-        <v>1685</v>
+        <v>1174</v>
       </c>
       <c r="H16" t="n">
-        <v>2.8</v>
+        <v>14.7</v>
       </c>
       <c r="I16" t="n">
-        <v>119</v>
+        <v>630</v>
       </c>
       <c r="J16" t="n">
         <v>23.5</v>
@@ -1274,16 +1274,16 @@
         <v>391</v>
       </c>
       <c r="F17" t="n">
-        <v>40.6</v>
+        <v>26.1</v>
       </c>
       <c r="G17" t="n">
-        <v>438</v>
+        <v>282</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>17.9</v>
       </c>
       <c r="I17" t="n">
-        <v>37</v>
+        <v>193</v>
       </c>
       <c r="J17" t="n">
         <v>19.8</v>
@@ -1324,16 +1324,16 @@
         <v>1618</v>
       </c>
       <c r="F18" t="n">
-        <v>36.3</v>
+        <v>26.8</v>
       </c>
       <c r="G18" t="n">
-        <v>1455</v>
+        <v>1073</v>
       </c>
       <c r="H18" t="n">
-        <v>10.9</v>
+        <v>20.4</v>
       </c>
       <c r="I18" t="n">
-        <v>436</v>
+        <v>818</v>
       </c>
       <c r="J18" t="n">
         <v>12.5</v>
@@ -1374,16 +1374,16 @@
         <v>127</v>
       </c>
       <c r="F19" t="n">
-        <v>25.2</v>
+        <v>23.7</v>
       </c>
       <c r="G19" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="H19" t="n">
-        <v>3.2</v>
+        <v>4.7</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
         <v>11</v>
@@ -1424,16 +1424,16 @@
         <v>153</v>
       </c>
       <c r="F20" t="n">
-        <v>27.2</v>
+        <v>19.7</v>
       </c>
       <c r="G20" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="H20" t="n">
-        <v>12.9</v>
+        <v>20.4</v>
       </c>
       <c r="I20" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="J20" t="n">
         <v>14</v>
@@ -1474,16 +1474,16 @@
         <v>75</v>
       </c>
       <c r="F21" t="n">
-        <v>27.9</v>
+        <v>25.2</v>
       </c>
       <c r="G21" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H21" t="n">
-        <v>10.3</v>
+        <v>12.9</v>
       </c>
       <c r="I21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
         <v>14.1</v>
@@ -1524,16 +1524,16 @@
         <v>326</v>
       </c>
       <c r="F22" t="n">
-        <v>40.5</v>
+        <v>30.5</v>
       </c>
       <c r="G22" t="n">
-        <v>347</v>
+        <v>261</v>
       </c>
       <c r="H22" t="n">
-        <v>9.800000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="I22" t="n">
-        <v>83</v>
+        <v>169</v>
       </c>
       <c r="J22" t="n">
         <v>11.6</v>
@@ -1574,16 +1574,16 @@
         <v>487</v>
       </c>
       <c r="F23" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H23" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
         <v>5.6</v>
@@ -1674,16 +1674,16 @@
         <v>327</v>
       </c>
       <c r="F25" t="n">
-        <v>23.2</v>
+        <v>22.7</v>
       </c>
       <c r="G25" t="n">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="H25" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
         <v>28.8</v>
@@ -1724,16 +1724,16 @@
         <v>260</v>
       </c>
       <c r="F26" t="n">
-        <v>34.4</v>
+        <v>19.2</v>
       </c>
       <c r="G26" t="n">
-        <v>575</v>
+        <v>320</v>
       </c>
       <c r="H26" t="n">
-        <v>19.5</v>
+        <v>34.7</v>
       </c>
       <c r="I26" t="n">
-        <v>325</v>
+        <v>580</v>
       </c>
       <c r="J26" t="n">
         <v>30.5</v>
@@ -1774,16 +1774,16 @@
         <v>3439</v>
       </c>
       <c r="F27" t="n">
-        <v>22.6</v>
+        <v>20.1</v>
       </c>
       <c r="G27" t="n">
-        <v>1195</v>
+        <v>1066</v>
       </c>
       <c r="H27" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="J27" t="n">
         <v>11</v>
@@ -1824,16 +1824,16 @@
         <v>949</v>
       </c>
       <c r="F28" t="n">
-        <v>14.9</v>
+        <v>14.5</v>
       </c>
       <c r="G28" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H28" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
         <v>7.8</v>
@@ -1874,16 +1874,16 @@
         <v>7297</v>
       </c>
       <c r="F29" t="n">
-        <v>21.5</v>
+        <v>14.8</v>
       </c>
       <c r="G29" t="n">
-        <v>2407</v>
+        <v>1655</v>
       </c>
       <c r="H29" t="n">
-        <v>4.7</v>
+        <v>11.4</v>
       </c>
       <c r="I29" t="n">
-        <v>527</v>
+        <v>1279</v>
       </c>
       <c r="J29" t="n">
         <v>8.699999999999999</v>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1514</v>
       </c>
       <c r="F30" t="n">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="G30" t="n">
-        <v>828</v>
+        <v>710</v>
       </c>
       <c r="H30" t="n">
-        <v>16.1</v>
+        <v>19.4</v>
       </c>
       <c r="I30" t="n">
-        <v>592</v>
+        <v>710</v>
       </c>
       <c r="J30" t="n">
         <v>20</v>
@@ -1949,7 +1949,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1974,16 +1974,16 @@
         <v>4295</v>
       </c>
       <c r="F31" t="n">
-        <v>20.1</v>
+        <v>16.8</v>
       </c>
       <c r="G31" t="n">
-        <v>1218</v>
+        <v>1015</v>
       </c>
       <c r="H31" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="I31" t="n">
-        <v>203</v>
+        <v>406</v>
       </c>
       <c r="J31" t="n">
         <v>5.6</v>
@@ -2024,16 +2024,16 @@
         <v>2478</v>
       </c>
       <c r="F32" t="n">
-        <v>27.6</v>
+        <v>26.3</v>
       </c>
       <c r="G32" t="n">
-        <v>1025</v>
+        <v>977</v>
       </c>
       <c r="H32" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="I32" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="J32" t="n">
         <v>4.5</v>
@@ -2074,16 +2074,16 @@
         <v>336</v>
       </c>
       <c r="F33" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="G33" t="n">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
         <v>1.7</v>
@@ -2124,16 +2124,16 @@
         <v>3933</v>
       </c>
       <c r="F34" t="n">
-        <v>16.1</v>
+        <v>15.5</v>
       </c>
       <c r="G34" t="n">
-        <v>911</v>
+        <v>879</v>
       </c>
       <c r="H34" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="J34" t="n">
         <v>14.1</v>
@@ -2174,16 +2174,16 @@
         <v>358</v>
       </c>
       <c r="F35" t="n">
-        <v>47.7</v>
+        <v>42.3</v>
       </c>
       <c r="G35" t="n">
-        <v>480</v>
+        <v>425</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>10.4</v>
       </c>
       <c r="I35" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="J35" t="n">
         <v>11.7</v>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2224,16 +2224,16 @@
         <v>30</v>
       </c>
       <c r="F36" t="n">
-        <v>22.9</v>
+        <v>18.6</v>
       </c>
       <c r="G36" t="n">
+        <v>11</v>
+      </c>
+      <c r="H36" t="n">
         <v>14</v>
       </c>
-      <c r="H36" t="n">
-        <v>9.699999999999999</v>
-      </c>
       <c r="I36" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J36" t="n">
         <v>18.6</v>
@@ -2274,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>10.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2324,16 +2324,16 @@
         <v>850</v>
       </c>
       <c r="F38" t="n">
-        <v>34.2</v>
+        <v>28.2</v>
       </c>
       <c r="G38" t="n">
-        <v>850</v>
+        <v>701</v>
       </c>
       <c r="H38" t="n">
-        <v>7.4</v>
+        <v>13.4</v>
       </c>
       <c r="I38" t="n">
-        <v>184</v>
+        <v>333</v>
       </c>
       <c r="J38" t="n">
         <v>24.2</v>
@@ -2374,13 +2374,13 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>12.7</v>
+        <v>12.4</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2424,16 +2424,16 @@
         <v>1902</v>
       </c>
       <c r="F40" t="n">
-        <v>22.4</v>
+        <v>21.6</v>
       </c>
       <c r="G40" t="n">
-        <v>631</v>
+        <v>608</v>
       </c>
       <c r="H40" t="n">
-        <v>5.5</v>
+        <v>6.3</v>
       </c>
       <c r="I40" t="n">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="J40" t="n">
         <v>4.6</v>
@@ -2474,16 +2474,16 @@
         <v>3145</v>
       </c>
       <c r="F41" t="n">
-        <v>34.7</v>
+        <v>28.9</v>
       </c>
       <c r="G41" t="n">
-        <v>2244</v>
+        <v>1866</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6</v>
+        <v>6.5</v>
       </c>
       <c r="I41" t="n">
-        <v>42</v>
+        <v>419</v>
       </c>
       <c r="J41" t="n">
         <v>15.9</v>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2524,16 +2524,16 @@
         <v>1236</v>
       </c>
       <c r="F42" t="n">
-        <v>33.8</v>
+        <v>33.5</v>
       </c>
       <c r="G42" t="n">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="H42" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J42" t="n">
         <v>16.5</v>
@@ -2574,16 +2574,16 @@
         <v>174</v>
       </c>
       <c r="F43" t="n">
-        <v>34.1</v>
+        <v>25.6</v>
       </c>
       <c r="G43" t="n">
-        <v>133</v>
+        <v>100</v>
       </c>
       <c r="H43" t="n">
-        <v>1.1</v>
+        <v>9.6</v>
       </c>
       <c r="I43" t="n">
-        <v>4</v>
+        <v>37</v>
       </c>
       <c r="J43" t="n">
         <v>20</v>
@@ -2624,16 +2624,16 @@
         <v>768</v>
       </c>
       <c r="F44" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="G44" t="n">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H44" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="I44" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J44" t="n">
         <v>10.7</v>
@@ -2674,16 +2674,16 @@
         <v>152</v>
       </c>
       <c r="F45" t="n">
-        <v>37.2</v>
+        <v>31.8</v>
       </c>
       <c r="G45" t="n">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="H45" t="n">
-        <v>8.5</v>
+        <v>13.9</v>
       </c>
       <c r="I45" t="n">
-        <v>48</v>
+        <v>79</v>
       </c>
       <c r="J45" t="n">
         <v>27.4</v>
@@ -2724,16 +2724,16 @@
         <v>1566</v>
       </c>
       <c r="F46" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="G46" t="n">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="H46" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="I46" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="J46" t="n">
         <v>12.9</v>
@@ -2774,16 +2774,16 @@
         <v>1558</v>
       </c>
       <c r="F47" t="n">
-        <v>34.7</v>
+        <v>28.6</v>
       </c>
       <c r="G47" t="n">
-        <v>1039</v>
+        <v>856</v>
       </c>
       <c r="H47" t="n">
-        <v>5.6</v>
+        <v>11.7</v>
       </c>
       <c r="I47" t="n">
-        <v>168</v>
+        <v>351</v>
       </c>
       <c r="J47" t="n">
         <v>7.7</v>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>22.8</v>
+        <v>21.5</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>26.6</v>
+        <v>27.8</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
@@ -2924,16 +2924,16 @@
         <v>9856</v>
       </c>
       <c r="F50" t="n">
-        <v>37.5</v>
+        <v>10.5</v>
       </c>
       <c r="G50" t="n">
-        <v>6768</v>
+        <v>1905</v>
       </c>
       <c r="H50" t="n">
-        <v>1.1</v>
+        <v>28</v>
       </c>
       <c r="I50" t="n">
-        <v>197</v>
+        <v>5059</v>
       </c>
       <c r="J50" t="n">
         <v>6.9</v>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3060,16 +3060,16 @@
         <v>374</v>
       </c>
       <c r="F2" t="n">
-        <v>48.9</v>
+        <v>47.8</v>
       </c>
       <c r="G2" t="n">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="I2" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="J2" t="n">
         <v>12</v>
@@ -3160,16 +3160,16 @@
         <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>23.1</v>
+        <v>15.4</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="H4" t="n">
-        <v>30.8</v>
+        <v>38.5</v>
       </c>
       <c r="I4" t="n">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="J4" t="n">
         <v>43.6</v>
@@ -3210,16 +3210,16 @@
         <v>402</v>
       </c>
       <c r="F5" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="G5" t="n">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="H5" t="n">
-        <v>6.7</v>
+        <v>8.9</v>
       </c>
       <c r="I5" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
         <v>32.2</v>
@@ -3260,16 +3260,16 @@
         <v>594</v>
       </c>
       <c r="F6" t="n">
-        <v>22.5</v>
+        <v>19.4</v>
       </c>
       <c r="G6" t="n">
-        <v>265</v>
+        <v>228</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="I6" t="n">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="J6" t="n">
         <v>24.8</v>
@@ -3310,16 +3310,16 @@
         <v>79</v>
       </c>
       <c r="F7" t="n">
-        <v>40.4</v>
+        <v>23.4</v>
       </c>
       <c r="G7" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="H7" t="n">
-        <v>19.1</v>
+        <v>36.2</v>
       </c>
       <c r="I7" t="n">
-        <v>55</v>
+        <v>104</v>
       </c>
       <c r="J7" t="n">
         <v>12.8</v>
@@ -3360,16 +3360,16 @@
         <v>211</v>
       </c>
       <c r="F8" t="n">
-        <v>32.2</v>
+        <v>18.6</v>
       </c>
       <c r="G8" t="n">
-        <v>286</v>
+        <v>166</v>
       </c>
       <c r="H8" t="n">
-        <v>16.9</v>
+        <v>30.5</v>
       </c>
       <c r="I8" t="n">
-        <v>151</v>
+        <v>271</v>
       </c>
       <c r="J8" t="n">
         <v>27.1</v>
@@ -3510,16 +3510,16 @@
         <v>875</v>
       </c>
       <c r="F11" t="n">
-        <v>41.1</v>
+        <v>17.8</v>
       </c>
       <c r="G11" t="n">
-        <v>772</v>
+        <v>335</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>28.8</v>
       </c>
       <c r="I11" t="n">
-        <v>103</v>
+        <v>541</v>
       </c>
       <c r="J11" t="n">
         <v>6.8</v>
@@ -3535,7 +3535,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3560,16 +3560,16 @@
         <v>1181</v>
       </c>
       <c r="F12" t="n">
-        <v>25.8</v>
+        <v>19.4</v>
       </c>
       <c r="G12" t="n">
-        <v>591</v>
+        <v>443</v>
       </c>
       <c r="H12" t="n">
-        <v>4.8</v>
+        <v>11.3</v>
       </c>
       <c r="I12" t="n">
-        <v>111</v>
+        <v>258</v>
       </c>
       <c r="J12" t="n">
         <v>17.7</v>
@@ -3660,16 +3660,16 @@
         <v>2700</v>
       </c>
       <c r="F14" t="n">
-        <v>26.7</v>
+        <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>1227</v>
+        <v>920</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>123</v>
+        <v>429</v>
       </c>
       <c r="J14" t="n">
         <v>12</v>
@@ -3685,7 +3685,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3710,16 +3710,16 @@
         <v>905</v>
       </c>
       <c r="F15" t="n">
-        <v>47.7</v>
+        <v>22.7</v>
       </c>
       <c r="G15" t="n">
-        <v>2111</v>
+        <v>1005</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5</v>
+        <v>29.5</v>
       </c>
       <c r="I15" t="n">
-        <v>201</v>
+        <v>1307</v>
       </c>
       <c r="J15" t="n">
         <v>27.3</v>
@@ -3760,16 +3760,16 @@
         <v>173</v>
       </c>
       <c r="F16" t="n">
-        <v>25.7</v>
+        <v>18.8</v>
       </c>
       <c r="G16" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H16" t="n">
-        <v>7.9</v>
+        <v>14.9</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="J16" t="n">
         <v>19.8</v>
@@ -3860,16 +3860,16 @@
         <v>26</v>
       </c>
       <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>15</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>6</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>20</v>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3910,16 +3910,16 @@
         <v>160</v>
       </c>
       <c r="F19" t="n">
-        <v>43.8</v>
+        <v>31.2</v>
       </c>
       <c r="G19" t="n">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="H19" t="n">
-        <v>6.9</v>
+        <v>19.4</v>
       </c>
       <c r="I19" t="n">
-        <v>29</v>
+        <v>82</v>
       </c>
       <c r="J19" t="n">
         <v>11.1</v>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -3960,16 +3960,16 @@
         <v>240</v>
       </c>
       <c r="F20" t="n">
-        <v>34.3</v>
+        <v>22.9</v>
       </c>
       <c r="G20" t="n">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>11.4</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="J20" t="n">
         <v>2.9</v>
@@ -4110,16 +4110,16 @@
         <v>257</v>
       </c>
       <c r="F23" t="n">
-        <v>19.6</v>
+        <v>17.9</v>
       </c>
       <c r="G23" t="n">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="H23" t="n">
-        <v>41.1</v>
+        <v>42.9</v>
       </c>
       <c r="I23" t="n">
-        <v>493</v>
+        <v>515</v>
       </c>
       <c r="J23" t="n">
         <v>17.9</v>
@@ -4160,16 +4160,16 @@
         <v>1296</v>
       </c>
       <c r="F24" t="n">
-        <v>29.5</v>
+        <v>29.1</v>
       </c>
       <c r="G24" t="n">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I24" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="J24" t="n">
         <v>13.5</v>
@@ -4360,16 +4360,16 @@
         <v>4584</v>
       </c>
       <c r="F28" t="n">
-        <v>11.6</v>
+        <v>9.1</v>
       </c>
       <c r="G28" t="n">
-        <v>665</v>
+        <v>525</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="J28" t="n">
         <v>8.5</v>
@@ -4410,16 +4410,16 @@
         <v>1197</v>
       </c>
       <c r="F29" t="n">
-        <v>20.9</v>
+        <v>19.3</v>
       </c>
       <c r="G29" t="n">
-        <v>351</v>
+        <v>324</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="J29" t="n">
         <v>7.8</v>
@@ -4510,16 +4510,16 @@
         <v>1697</v>
       </c>
       <c r="F31" t="n">
-        <v>30.8</v>
+        <v>30.1</v>
       </c>
       <c r="G31" t="n">
-        <v>1103</v>
+        <v>1078</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
         <v>21.8</v>
@@ -4560,16 +4560,16 @@
         <v>173</v>
       </c>
       <c r="F32" t="n">
-        <v>31.2</v>
+        <v>25</v>
       </c>
       <c r="G32" t="n">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
         <v>3.1</v>
@@ -4610,16 +4610,16 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>78.90000000000001</v>
+        <v>63.2</v>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H33" t="n">
-        <v>10.5</v>
+        <v>26.3</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
         <v>10.5</v>
@@ -4710,16 +4710,16 @@
         <v>712</v>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>17.4</v>
       </c>
       <c r="G35" t="n">
-        <v>375</v>
+        <v>327</v>
       </c>
       <c r="H35" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I35" t="n">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="J35" t="n">
         <v>36.4</v>
@@ -4810,16 +4810,16 @@
         <v>336</v>
       </c>
       <c r="F37" t="n">
-        <v>19.3</v>
+        <v>12.5</v>
       </c>
       <c r="G37" t="n">
-        <v>197</v>
+        <v>128</v>
       </c>
       <c r="H37" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="J37" t="n">
         <v>46.6</v>
@@ -5110,16 +5110,16 @@
         <v>875</v>
       </c>
       <c r="F43" t="n">
-        <v>20.2</v>
+        <v>19.7</v>
       </c>
       <c r="G43" t="n">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="I43" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J43" t="n">
         <v>12.1</v>
@@ -5310,16 +5310,16 @@
         <v>9536</v>
       </c>
       <c r="F47" t="n">
-        <v>29.6</v>
+        <v>4.9</v>
       </c>
       <c r="G47" t="n">
-        <v>4551</v>
+        <v>759</v>
       </c>
       <c r="H47" t="n">
-        <v>2.1</v>
+        <v>26.8</v>
       </c>
       <c r="I47" t="n">
-        <v>325</v>
+        <v>4118</v>
       </c>
       <c r="J47" t="n">
         <v>6.3</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5446,13 +5446,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>42.6</v>
+        <v>31.1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>14.8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -5496,16 +5496,16 @@
         <v>840</v>
       </c>
       <c r="F3" t="n">
-        <v>15.6</v>
+        <v>8.1</v>
       </c>
       <c r="G3" t="n">
-        <v>229</v>
+        <v>119</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="I3" t="n">
-        <v>161</v>
+        <v>272</v>
       </c>
       <c r="J3" t="n">
         <v>16.2</v>
@@ -5546,16 +5546,16 @@
         <v>368</v>
       </c>
       <c r="F4" t="n">
-        <v>20.1</v>
+        <v>16.6</v>
       </c>
       <c r="G4" t="n">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>8.9</v>
       </c>
       <c r="I4" t="n">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="J4" t="n">
         <v>19.5</v>
@@ -5646,16 +5646,16 @@
         <v>117</v>
       </c>
       <c r="F6" t="n">
-        <v>62.1</v>
+        <v>39.4</v>
       </c>
       <c r="G6" t="n">
-        <v>229</v>
+        <v>145</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5</v>
+        <v>24.2</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="J6" t="n">
         <v>4.5</v>
@@ -5671,7 +5671,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5696,16 +5696,16 @@
         <v>432</v>
       </c>
       <c r="F7" t="n">
-        <v>29.3</v>
+        <v>20.5</v>
       </c>
       <c r="G7" t="n">
-        <v>210</v>
+        <v>147</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>12.4</v>
       </c>
       <c r="I7" t="n">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="J7" t="n">
         <v>6.8</v>
@@ -5746,16 +5746,16 @@
         <v>315</v>
       </c>
       <c r="F8" t="n">
-        <v>34.3</v>
+        <v>29.9</v>
       </c>
       <c r="G8" t="n">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="J8" t="n">
         <v>17.9</v>
@@ -5771,7 +5771,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5796,16 +5796,16 @@
         <v>1326</v>
       </c>
       <c r="F9" t="n">
-        <v>16.1</v>
+        <v>15.1</v>
       </c>
       <c r="G9" t="n">
-        <v>278</v>
+        <v>262</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="I9" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="J9" t="n">
         <v>5.5</v>
@@ -5846,16 +5846,16 @@
         <v>312</v>
       </c>
       <c r="F10" t="n">
-        <v>23.4</v>
+        <v>16.9</v>
       </c>
       <c r="G10" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
         <v>18.2</v>
@@ -5871,7 +5871,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5896,19 +5896,19 @@
         <v>42</v>
       </c>
       <c r="F11" t="n">
-        <v>34.4</v>
+        <v>25</v>
       </c>
       <c r="G11" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J11" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="K11" t="n">
         <v>17</v>
@@ -5921,7 +5921,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -5946,16 +5946,16 @@
         <v>296</v>
       </c>
       <c r="F12" t="n">
-        <v>38.2</v>
+        <v>29.2</v>
       </c>
       <c r="G12" t="n">
-        <v>280</v>
+        <v>214</v>
       </c>
       <c r="H12" t="n">
-        <v>5.6</v>
+        <v>14.6</v>
       </c>
       <c r="I12" t="n">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="J12" t="n">
         <v>15.7</v>
@@ -5996,16 +5996,16 @@
         <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>45.1</v>
+        <v>27.1</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>21.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>9.5</v>
@@ -6021,7 +6021,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6046,13 +6046,13 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>26.7</v>
+        <v>13.3</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>13.3</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -6096,16 +6096,16 @@
         <v>57</v>
       </c>
       <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
+      <c r="H15" t="n">
         <v>16</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>11</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
-      <c r="I15" t="n">
-        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -6196,16 +6196,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>14.3</v>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>35.7</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -6246,16 +6246,16 @@
         <v>169</v>
       </c>
       <c r="F18" t="n">
-        <v>23.5</v>
+        <v>20.6</v>
       </c>
       <c r="G18" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="H18" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="I18" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="J18" t="n">
         <v>2.9</v>
@@ -6346,16 +6346,16 @@
         <v>31</v>
       </c>
       <c r="F20" t="n">
-        <v>48.4</v>
+        <v>43.5</v>
       </c>
       <c r="G20" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="H20" t="n">
-        <v>14.5</v>
+        <v>19.4</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
         <v>11.3</v>
@@ -6396,16 +6396,16 @@
         <v>28</v>
       </c>
       <c r="F21" t="n">
-        <v>33.8</v>
+        <v>30.8</v>
       </c>
       <c r="G21" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H21" t="n">
-        <v>26.2</v>
+        <v>29.2</v>
       </c>
       <c r="I21" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J21" t="n">
         <v>21.5</v>
@@ -6446,16 +6446,16 @@
         <v>297</v>
       </c>
       <c r="F22" t="n">
-        <v>21.2</v>
+        <v>20.6</v>
       </c>
       <c r="G22" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H22" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J22" t="n">
         <v>12.7</v>
@@ -6496,16 +6496,16 @@
         <v>67</v>
       </c>
       <c r="F23" t="n">
-        <v>17.8</v>
+        <v>16.6</v>
       </c>
       <c r="G23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" t="n">
         <v>10.1</v>
@@ -6546,16 +6546,16 @@
         <v>1598</v>
       </c>
       <c r="F24" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="G24" t="n">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="J24" t="n">
         <v>2.3</v>
@@ -6696,16 +6696,16 @@
         <v>876</v>
       </c>
       <c r="F27" t="n">
-        <v>26.3</v>
+        <v>24.8</v>
       </c>
       <c r="G27" t="n">
-        <v>345</v>
+        <v>326</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4</v>
+        <v>1.8</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
         <v>6.6</v>
@@ -6796,16 +6796,16 @@
         <v>931</v>
       </c>
       <c r="F29" t="n">
-        <v>30.8</v>
+        <v>30.5</v>
       </c>
       <c r="G29" t="n">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
         <v>19.7</v>
@@ -7096,16 +7096,16 @@
         <v>167</v>
       </c>
       <c r="F35" t="n">
-        <v>30.6</v>
+        <v>24.7</v>
       </c>
       <c r="G35" t="n">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
         <v>20</v>
@@ -7146,13 +7146,13 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>19.2</v>
+        <v>15.4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>5.8</v>
+        <v>9.6</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -7196,13 +7196,13 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>35.1</v>
+        <v>28.6</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -7296,16 +7296,16 @@
         <v>56</v>
       </c>
       <c r="F39" t="n">
-        <v>40.7</v>
+        <v>33.3</v>
       </c>
       <c r="G39" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H39" t="n">
-        <v>11.9</v>
+        <v>19.2</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="J39" t="n">
         <v>16.4</v>
@@ -7396,16 +7396,16 @@
         <v>987</v>
       </c>
       <c r="F41" t="n">
-        <v>27.1</v>
+        <v>26</v>
       </c>
       <c r="G41" t="n">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="H41" t="n">
-        <v>4.2</v>
+        <v>5.2</v>
       </c>
       <c r="I41" t="n">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="J41" t="n">
         <v>5.2</v>
@@ -7546,16 +7546,16 @@
         <v>304</v>
       </c>
       <c r="F44" t="n">
-        <v>40.2</v>
+        <v>39.2</v>
       </c>
       <c r="G44" t="n">
-        <v>848</v>
+        <v>826</v>
       </c>
       <c r="H44" t="n">
-        <v>13.4</v>
+        <v>14.4</v>
       </c>
       <c r="I44" t="n">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="J44" t="n">
         <v>32</v>
@@ -7646,16 +7646,16 @@
         <v>900</v>
       </c>
       <c r="F46" t="n">
-        <v>24.2</v>
+        <v>9.1</v>
       </c>
       <c r="G46" t="n">
-        <v>343</v>
+        <v>129</v>
       </c>
       <c r="H46" t="n">
-        <v>1.3</v>
+        <v>16.4</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>232</v>
       </c>
       <c r="J46" t="n">
         <v>11</v>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -7782,16 +7782,16 @@
         <v>232</v>
       </c>
       <c r="F2" t="n">
-        <v>11.3</v>
+        <v>8</v>
       </c>
       <c r="G2" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H2" t="n">
-        <v>4</v>
+        <v>7.3</v>
       </c>
       <c r="I2" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J2" t="n">
         <v>25.9</v>
@@ -7832,16 +7832,16 @@
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>25.5</v>
+        <v>19.6</v>
       </c>
       <c r="G3" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J3" t="n">
         <v>52.9</v>
@@ -7882,16 +7882,16 @@
         <v>1067</v>
       </c>
       <c r="F4" t="n">
-        <v>17.9</v>
+        <v>17.1</v>
       </c>
       <c r="G4" t="n">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="I4" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="J4" t="n">
         <v>15.4</v>
@@ -7932,16 +7932,16 @@
         <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>17.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>15.9</v>
+        <v>24.6</v>
       </c>
       <c r="I5" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J5" t="n">
         <v>26.1</v>
@@ -7982,16 +7982,16 @@
         <v>147</v>
       </c>
       <c r="F6" t="n">
-        <v>34.4</v>
+        <v>31.2</v>
       </c>
       <c r="G6" t="n">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="I6" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J6" t="n">
         <v>21.9</v>
@@ -8032,16 +8032,16 @@
         <v>1329</v>
       </c>
       <c r="F7" t="n">
-        <v>22.7</v>
+        <v>16.5</v>
       </c>
       <c r="G7" t="n">
-        <v>499</v>
+        <v>364</v>
       </c>
       <c r="H7" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="I7" t="n">
-        <v>118</v>
+        <v>254</v>
       </c>
       <c r="J7" t="n">
         <v>11.5</v>
@@ -8057,7 +8057,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -8082,16 +8082,16 @@
         <v>1580</v>
       </c>
       <c r="F8" t="n">
-        <v>28.6</v>
+        <v>27.8</v>
       </c>
       <c r="G8" t="n">
-        <v>770</v>
+        <v>750</v>
       </c>
       <c r="H8" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="J8" t="n">
         <v>9.4</v>
@@ -8282,13 +8282,13 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>9.5</v>
+        <v>8.1</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -8332,16 +8332,16 @@
         <v>1998</v>
       </c>
       <c r="F13" t="n">
-        <v>21.7</v>
+        <v>19.9</v>
       </c>
       <c r="G13" t="n">
-        <v>754</v>
+        <v>691</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="J13" t="n">
         <v>19.2</v>
@@ -8382,16 +8382,16 @@
         <v>385</v>
       </c>
       <c r="F14" t="n">
-        <v>25.6</v>
+        <v>24.8</v>
       </c>
       <c r="G14" t="n">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="H14" t="n">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="J14" t="n">
         <v>14</v>
@@ -8432,16 +8432,16 @@
         <v>549</v>
       </c>
       <c r="F15" t="n">
-        <v>26.1</v>
+        <v>20.1</v>
       </c>
       <c r="G15" t="n">
-        <v>287</v>
+        <v>221</v>
       </c>
       <c r="H15" t="n">
-        <v>9.699999999999999</v>
+        <v>15.7</v>
       </c>
       <c r="I15" t="n">
-        <v>106</v>
+        <v>172</v>
       </c>
       <c r="J15" t="n">
         <v>14.2</v>
@@ -8482,16 +8482,16 @@
         <v>1833</v>
       </c>
       <c r="F16" t="n">
-        <v>36</v>
+        <v>34.9</v>
       </c>
       <c r="G16" t="n">
-        <v>1235</v>
+        <v>1195</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="I16" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J16" t="n">
         <v>9.300000000000001</v>
@@ -8582,16 +8582,16 @@
         <v>143</v>
       </c>
       <c r="F18" t="n">
-        <v>25.4</v>
+        <v>4.4</v>
       </c>
       <c r="G18" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="J18" t="n">
         <v>15.1</v>
@@ -8607,7 +8607,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
